--- a/data/exports/prod-portfolio_intelligence.xlsx
+++ b/data/exports/prod-portfolio_intelligence.xlsx
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7466.139999999999</v>
+        <v>7478.04</v>
       </c>
       <c r="C2" t="n">
-        <v>28.78</v>
+        <v>28.81</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5958.6</v>
+        <v>5979.36</v>
       </c>
       <c r="C3" t="n">
-        <v>22.97</v>
+        <v>23.03</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5551.5</v>
+        <v>5542.5</v>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>21.35</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3653.58</v>
+        <v>3657.78</v>
       </c>
       <c r="C5" t="n">
-        <v>14.08</v>
+        <v>14.09</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3313.9</v>
+        <v>3303.05</v>
       </c>
       <c r="C6" t="n">
-        <v>12.77</v>
+        <v>12.72</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         <v>80</v>
       </c>
       <c r="D2" t="n">
-        <v>964</v>
+        <v>968.8</v>
       </c>
       <c r="E2" t="n">
-        <v>258.69</v>
+        <v>263.49</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9024</v>
+        <v>0.9023</v>
       </c>
     </row>
     <row r="3">
@@ -971,13 +971,13 @@
         <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>530.2</v>
+        <v>532.84</v>
       </c>
       <c r="E3" t="n">
-        <v>142.28</v>
+        <v>144.92</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8878</v>
+        <v>0.8877</v>
       </c>
     </row>
     <row r="4">
@@ -995,13 +995,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>26.78</v>
+        <v>26.8</v>
       </c>
       <c r="E4" t="n">
-        <v>14.94</v>
+        <v>14.96</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8333</v>
+        <v>0.8334</v>
       </c>
     </row>
     <row r="5">
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>259.82</v>
+        <v>259.07</v>
       </c>
       <c r="D5" t="n">
-        <v>3479.02</v>
+        <v>3471.56</v>
       </c>
       <c r="E5" t="n">
-        <v>2017.21</v>
+        <v>2013.97</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0389</v>
+        <v>1.0385</v>
       </c>
     </row>
     <row r="6">
@@ -1043,10 +1043,10 @@
         <v>80</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>968.8</v>
       </c>
       <c r="E6" t="n">
-        <v>258.69</v>
+        <v>263.49</v>
       </c>
       <c r="F6" t="n">
         <v>0.5155999999999999</v>
@@ -1067,13 +1067,13 @@
         <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>530.2</v>
+        <v>532.84</v>
       </c>
       <c r="E7" t="n">
-        <v>142.28</v>
+        <v>144.92</v>
       </c>
       <c r="F7" t="n">
-        <v>0.501</v>
+        <v>0.5009</v>
       </c>
     </row>
     <row r="8">
@@ -1091,10 +1091,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78</v>
+        <v>26.8</v>
       </c>
       <c r="E8" t="n">
-        <v>14.94</v>
+        <v>14.96</v>
       </c>
       <c r="F8" t="n">
         <v>0.4383</v>
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>259.82</v>
+        <v>259.07</v>
       </c>
       <c r="D9" t="n">
-        <v>3479.02</v>
+        <v>3471.56</v>
       </c>
       <c r="E9" t="n">
-        <v>2017.21</v>
+        <v>2013.97</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6575</v>
+        <v>0.657</v>
       </c>
     </row>
     <row r="10">
@@ -1139,10 +1139,10 @@
         <v>80</v>
       </c>
       <c r="D10" t="n">
-        <v>964</v>
+        <v>968.8</v>
       </c>
       <c r="E10" t="n">
-        <v>258.69</v>
+        <v>263.49</v>
       </c>
       <c r="F10" t="n">
         <v>0.5656</v>
@@ -1163,10 +1163,10 @@
         <v>44</v>
       </c>
       <c r="D11" t="n">
-        <v>530.2</v>
+        <v>532.84</v>
       </c>
       <c r="E11" t="n">
-        <v>142.28</v>
+        <v>144.92</v>
       </c>
       <c r="F11" t="n">
         <v>0.5217000000000001</v>
@@ -1187,10 +1187,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>26.78</v>
+        <v>26.8</v>
       </c>
       <c r="E12" t="n">
-        <v>14.94</v>
+        <v>14.96</v>
       </c>
       <c r="F12" t="n">
         <v>0.4383</v>
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>259.82</v>
+        <v>259.07</v>
       </c>
       <c r="D13" t="n">
-        <v>3479.02</v>
+        <v>3471.56</v>
       </c>
       <c r="E13" t="n">
-        <v>2017.21</v>
+        <v>2013.97</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0434</v>
+        <v>1.0417</v>
       </c>
     </row>
   </sheetData>
@@ -1524,19 +1524,19 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>609.14</v>
+        <v>609.63</v>
       </c>
       <c r="L2" t="n">
-        <v>3654.84</v>
+        <v>3657.78</v>
       </c>
       <c r="M2" t="n">
         <v>3167.86</v>
       </c>
       <c r="N2" t="n">
-        <v>486.98</v>
+        <v>489.92</v>
       </c>
       <c r="O2" t="n">
-        <v>15.37</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="3">
@@ -1571,19 +1571,19 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>74.05</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>3258.2</v>
+        <v>3251.6</v>
       </c>
       <c r="M3" t="n">
         <v>1711.47</v>
       </c>
       <c r="N3" t="n">
-        <v>1546.73</v>
+        <v>1540.13</v>
       </c>
       <c r="O3" t="n">
-        <v>90.37</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1618,19 +1618,19 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>497</v>
+        <v>498.28</v>
       </c>
       <c r="L4" t="n">
-        <v>5964</v>
+        <v>5979.36</v>
       </c>
       <c r="M4" t="n">
         <v>1859.52</v>
       </c>
       <c r="N4" t="n">
-        <v>4104.48</v>
+        <v>4119.84</v>
       </c>
       <c r="O4" t="n">
-        <v>220.73</v>
+        <v>221.55</v>
       </c>
     </row>
     <row r="5">
@@ -1665,19 +1665,19 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>107.07</v>
+        <v>106.55</v>
       </c>
       <c r="L5" t="n">
-        <v>3319.17</v>
+        <v>3303.05</v>
       </c>
       <c r="M5" t="n">
         <v>2074.09</v>
       </c>
       <c r="N5" t="n">
-        <v>1245.08</v>
+        <v>1228.96</v>
       </c>
       <c r="O5" t="n">
-        <v>60.03</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="6">
@@ -1712,19 +1712,19 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>74.05</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>2295.55</v>
+        <v>2290.9</v>
       </c>
       <c r="M6" t="n">
         <v>1936.33</v>
       </c>
       <c r="N6" t="n">
-        <v>359.22</v>
+        <v>354.57</v>
       </c>
       <c r="O6" t="n">
-        <v>18.55</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="7">
@@ -1759,19 +1759,19 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>12.06</v>
+        <v>12.11</v>
       </c>
       <c r="L7" t="n">
-        <v>964.8</v>
+        <v>968.8</v>
       </c>
       <c r="M7" t="n">
         <v>705.3099999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>259.49</v>
+        <v>263.49</v>
       </c>
       <c r="O7" t="n">
-        <v>36.79</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="8">
@@ -1806,19 +1806,19 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>12.06</v>
+        <v>12.11</v>
       </c>
       <c r="L8" t="n">
-        <v>530.64</v>
+        <v>532.84</v>
       </c>
       <c r="M8" t="n">
         <v>387.92</v>
       </c>
       <c r="N8" t="n">
-        <v>142.72</v>
+        <v>144.92</v>
       </c>
       <c r="O8" t="n">
-        <v>36.79</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="9">
@@ -1853,19 +1853,19 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>13.39</v>
+        <v>13.4</v>
       </c>
       <c r="L9" t="n">
-        <v>5945.16</v>
+        <v>5949.6</v>
       </c>
       <c r="M9" t="n">
         <v>2498.03</v>
       </c>
       <c r="N9" t="n">
-        <v>3447.13</v>
+        <v>3451.57</v>
       </c>
       <c r="O9" t="n">
-        <v>137.99</v>
+        <v>138.17</v>
       </c>
     </row>
     <row r="10">
@@ -1900,19 +1900,19 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>13.39</v>
+        <v>13.4</v>
       </c>
       <c r="L10" t="n">
-        <v>26.78</v>
+        <v>26.8</v>
       </c>
       <c r="M10" t="n">
         <v>11.84</v>
       </c>
       <c r="N10" t="n">
-        <v>14.94</v>
+        <v>14.96</v>
       </c>
       <c r="O10" t="n">
-        <v>126.18</v>
+        <v>126.35</v>
       </c>
     </row>
   </sheetData>
@@ -1991,13 +1991,13 @@
         <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>964.8</v>
+        <v>968.8</v>
       </c>
       <c r="D2" t="n">
-        <v>259.49</v>
+        <v>263.49</v>
       </c>
       <c r="E2" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="F2" t="n">
         <v>0.5155999999999999</v>
@@ -2006,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.158</v>
+        <v>0.1583</v>
       </c>
       <c r="I2" t="n">
         <v>0.0331</v>
@@ -2027,22 +2027,22 @@
         <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>530.64</v>
+        <v>532.84</v>
       </c>
       <c r="D3" t="n">
-        <v>142.72</v>
+        <v>144.92</v>
       </c>
       <c r="E3" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="F3" t="n">
-        <v>0.501</v>
+        <v>0.5009</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0849</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>0.0331</v>
@@ -2063,19 +2063,19 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>26.78</v>
+        <v>26.8</v>
       </c>
       <c r="D4" t="n">
-        <v>14.94</v>
+        <v>14.96</v>
       </c>
       <c r="E4" t="n">
-        <v>7.47</v>
+        <v>7.48</v>
       </c>
       <c r="F4" t="n">
         <v>0.4383</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9875</v>
+        <v>0.9877</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2096,25 +2096,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>259.73</v>
+        <v>259.07</v>
       </c>
       <c r="C5" t="n">
-        <v>3477.78</v>
+        <v>3471.56</v>
       </c>
       <c r="D5" t="n">
-        <v>2016.49</v>
+        <v>2013.97</v>
       </c>
       <c r="E5" t="n">
-        <v>7.76</v>
+        <v>7.77</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6573</v>
+        <v>0.657</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9867</v>
+        <v>0.9868</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9968</v>
+        <v>0.995</v>
       </c>
       <c r="I5" t="n">
         <v>0.0331</v>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107.04</v>
+        <v>106.54</v>
       </c>
       <c r="C2" t="n">
-        <v>102.39</v>
+        <v>102.38</v>
       </c>
       <c r="D2" t="n">
         <v>100.14</v>
       </c>
       <c r="E2" t="n">
-        <v>35.86</v>
+        <v>35.42</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -2256,13 +2256,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8207</v>
+        <v>0.8229</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6414</v>
+        <v>0.6458</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8119</v>
+        <v>0.8126</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>12.79</v>
+        <v>12.72</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8721</v>
+        <v>0.8728</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.05</v>
+        <v>12.11</v>
       </c>
       <c r="C3" t="n">
         <v>11.44</v>
@@ -2311,7 +2311,7 @@
         <v>5.86</v>
       </c>
       <c r="E3" t="n">
-        <v>35.82</v>
+        <v>35.95</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -2320,13 +2320,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8209</v>
+        <v>0.8202</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6418</v>
+        <v>0.6405</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7778</v>
+        <v>0.7776</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>28.77</v>
+        <v>28.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7123</v>
+        <v>0.712</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>213.55</v>
+        <v>213.63</v>
       </c>
       <c r="C4" t="n">
-        <v>197.47</v>
+        <v>197.48</v>
       </c>
       <c r="D4" t="n">
         <v>187.18</v>
       </c>
       <c r="E4" t="n">
-        <v>62.69</v>
+        <v>62.77</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -2384,13 +2384,13 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6866</v>
+        <v>0.6862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3731</v>
+        <v>0.3723</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7755</v>
+        <v>0.7753</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>22.97</v>
+        <v>23.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7703</v>
+        <v>0.7695</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>497.11</v>
+        <v>498.42</v>
       </c>
       <c r="C5" t="n">
-        <v>309.26</v>
+        <v>309.29</v>
       </c>
       <c r="D5" t="n">
-        <v>232.5</v>
+        <v>232.51</v>
       </c>
       <c r="E5" t="n">
-        <v>76.7</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -2448,13 +2448,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6165</v>
+        <v>0.6159</v>
       </c>
       <c r="I5" t="n">
-        <v>0.233</v>
+        <v>0.2318</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7534</v>
+        <v>0.7531</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>22.97</v>
+        <v>23.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7703</v>
+        <v>0.7695</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>262.3</v>
+        <v>262.83</v>
       </c>
       <c r="C6" t="n">
-        <v>243.02</v>
+        <v>243.03</v>
       </c>
       <c r="D6" t="n">
         <v>230.75</v>
       </c>
       <c r="E6" t="n">
-        <v>37.62</v>
+        <v>38.06</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -2512,13 +2512,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8119</v>
+        <v>0.8097</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6238</v>
+        <v>0.6194</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7532</v>
+        <v>0.7526</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2558,16 +2558,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220.11</v>
+        <v>219.68</v>
       </c>
       <c r="C7" t="n">
-        <v>208.2</v>
+        <v>208.19</v>
       </c>
       <c r="D7" t="n">
         <v>204.14</v>
       </c>
       <c r="E7" t="n">
-        <v>39.88</v>
+        <v>39.66</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -2576,13 +2576,13 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8006</v>
+        <v>0.8017</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6012</v>
+        <v>0.6034</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7518</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>188.49</v>
+        <v>188.37</v>
       </c>
       <c r="C8" t="n">
         <v>152.77</v>
@@ -2631,7 +2631,7 @@
         <v>126.99</v>
       </c>
       <c r="E8" t="n">
-        <v>42.83</v>
+        <v>42.69</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -2640,13 +2640,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7859</v>
+        <v>0.7866</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5717</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.744</v>
+        <v>0.7442</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2682,20 +2682,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.36</v>
+        <v>159.22</v>
       </c>
       <c r="C9" t="n">
-        <v>77.5</v>
+        <v>147.58</v>
       </c>
       <c r="D9" t="n">
-        <v>72.2</v>
+        <v>139.9</v>
       </c>
       <c r="E9" t="n">
-        <v>63.03</v>
+        <v>42.66</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -2704,13 +2704,13 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6848</v>
+        <v>0.7867</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3697</v>
+        <v>0.5734</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7421</v>
+        <v>0.7409</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2740,26 +2740,26 @@
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5778</v>
+        <v>0.3661</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158.98</v>
+        <v>80.48</v>
       </c>
       <c r="C10" t="n">
-        <v>147.57</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>139.9</v>
+        <v>72.2</v>
       </c>
       <c r="E10" t="n">
-        <v>42.48</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -2768,13 +2768,13 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7876</v>
+        <v>0.6798</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5752</v>
+        <v>0.3596</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7412</v>
+        <v>0.7406</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>0.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3661</v>
+        <v>0.5778</v>
       </c>
     </row>
     <row r="11">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>326.99</v>
+        <v>327.23</v>
       </c>
       <c r="C11" t="n">
         <v>304.39</v>
@@ -2823,7 +2823,7 @@
         <v>208.61</v>
       </c>
       <c r="E11" t="n">
-        <v>45.25</v>
+        <v>45.32</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -2832,13 +2832,13 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7734</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5475</v>
+        <v>0.5468</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7405</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>181.12</v>
+        <v>184.18</v>
       </c>
       <c r="C12" t="n">
-        <v>143.36</v>
+        <v>143.42</v>
       </c>
       <c r="D12" t="n">
-        <v>63.76</v>
+        <v>63.77</v>
       </c>
       <c r="E12" t="n">
-        <v>50.15</v>
+        <v>50.99</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -2896,13 +2896,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7492</v>
+        <v>0.745</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4985</v>
+        <v>0.4901</v>
       </c>
       <c r="J12" t="n">
-        <v>0.739</v>
+        <v>0.7378</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2938,20 +2938,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>382.13</v>
+        <v>13.39</v>
       </c>
       <c r="C13" t="n">
-        <v>340.45</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>296.72</v>
+        <v>6.92</v>
       </c>
       <c r="E13" t="n">
-        <v>48.32</v>
+        <v>59.22</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -2960,13 +2960,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7584</v>
+        <v>0.7039</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5168</v>
+        <v>0.4078</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7367</v>
+        <v>0.7366</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2975,14 +2975,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OPTICAL_NETWORKING</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.712</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2993,29 +2993,29 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3945</v>
+        <v>0.3906</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13.39</v>
+        <v>382.81</v>
       </c>
       <c r="C14" t="n">
-        <v>9.109999999999999</v>
+        <v>340.47</v>
       </c>
       <c r="D14" t="n">
-        <v>6.92</v>
+        <v>296.72</v>
       </c>
       <c r="E14" t="n">
-        <v>59.22</v>
+        <v>48.86</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -3024,13 +3024,13 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7039</v>
+        <v>0.7557</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4078</v>
+        <v>0.5114</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7366</v>
+        <v>0.7359</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3039,14 +3039,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OPTICAL_NETWORKING</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>28.77</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7123</v>
+        <v>1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3906</v>
+        <v>0.3945</v>
       </c>
     </row>
     <row r="15">
@@ -3070,16 +3070,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>405.02</v>
+        <v>404.58</v>
       </c>
       <c r="C15" t="n">
-        <v>390.29</v>
+        <v>390.28</v>
       </c>
       <c r="D15" t="n">
         <v>362.34</v>
       </c>
       <c r="E15" t="n">
-        <v>48.4</v>
+        <v>48.24</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -3088,13 +3088,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.758</v>
+        <v>0.7588</v>
       </c>
       <c r="I15" t="n">
-        <v>0.516</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.735</v>
+        <v>0.7352</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3134,16 +3134,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>422.18</v>
+        <v>422.67</v>
       </c>
       <c r="C16" t="n">
-        <v>378.97</v>
+        <v>378.98</v>
       </c>
       <c r="D16" t="n">
-        <v>349.49</v>
+        <v>349.5</v>
       </c>
       <c r="E16" t="n">
-        <v>47.76</v>
+        <v>47.98</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -3152,13 +3152,13 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7612</v>
+        <v>0.7601</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5224</v>
+        <v>0.5202</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7287</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
+        <v>54.06</v>
       </c>
       <c r="C17" t="n">
         <v>46.04</v>
@@ -3207,7 +3207,7 @@
         <v>32.66</v>
       </c>
       <c r="E17" t="n">
-        <v>55.97</v>
+        <v>56.08</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -3216,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7202</v>
+        <v>0.7196</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4403</v>
+        <v>0.4392</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7244</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -3262,16 +3262,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>383.44</v>
+        <v>384.84</v>
       </c>
       <c r="C18" t="n">
-        <v>343.72</v>
+        <v>343.75</v>
       </c>
       <c r="D18" t="n">
-        <v>229.64</v>
+        <v>229.65</v>
       </c>
       <c r="E18" t="n">
-        <v>57.19</v>
+        <v>57.51</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -3280,13 +3280,13 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7141</v>
+        <v>0.7124</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4281</v>
+        <v>0.4249</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7198</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1602.72</v>
+        <v>1612.99</v>
       </c>
       <c r="C19" t="n">
-        <v>1023.89</v>
+        <v>1024.09</v>
       </c>
       <c r="D19" t="n">
-        <v>464.35</v>
+        <v>464.4</v>
       </c>
       <c r="E19" t="n">
-        <v>60.1</v>
+        <v>60.52</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -3344,13 +3344,13 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6995</v>
+        <v>0.6974</v>
       </c>
       <c r="I19" t="n">
-        <v>0.399</v>
+        <v>0.3948</v>
       </c>
       <c r="J19" t="n">
-        <v>0.72</v>
+        <v>0.7194</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>217.6</v>
+        <v>219.68</v>
       </c>
       <c r="C20" t="n">
-        <v>151.83</v>
+        <v>151.88</v>
       </c>
       <c r="D20" t="n">
-        <v>143.63</v>
+        <v>143.64</v>
       </c>
       <c r="E20" t="n">
-        <v>57.82</v>
+        <v>58.48</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -3408,13 +3408,13 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7109</v>
+        <v>0.7076</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4218</v>
+        <v>0.4152</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7192</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>120.96</v>
+        <v>122.49</v>
       </c>
       <c r="C21" t="n">
-        <v>77.95</v>
+        <v>77.98</v>
       </c>
       <c r="D21" t="n">
-        <v>47.68</v>
+        <v>47.69</v>
       </c>
       <c r="E21" t="n">
-        <v>60.16</v>
+        <v>61.1</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -3472,13 +3472,13 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6992</v>
+        <v>0.6945</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3984</v>
+        <v>0.389</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7181</v>
+        <v>0.7167</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3518,16 +3518,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>454.01</v>
+        <v>455.4</v>
       </c>
       <c r="C22" t="n">
-        <v>401.69</v>
+        <v>401.72</v>
       </c>
       <c r="D22" t="n">
-        <v>381.05</v>
+        <v>381.06</v>
       </c>
       <c r="E22" t="n">
-        <v>58.83</v>
+        <v>59.34</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -3536,13 +3536,13 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7059</v>
+        <v>0.7033</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4117</v>
+        <v>0.4066</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7154</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3582,16 +3582,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>412.02</v>
+        <v>412.83</v>
       </c>
       <c r="C23" t="n">
-        <v>374.57</v>
+        <v>374.58</v>
       </c>
       <c r="D23" t="n">
-        <v>317.63</v>
+        <v>317.64</v>
       </c>
       <c r="E23" t="n">
-        <v>57.49</v>
+        <v>57.78</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -3600,13 +3600,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7126</v>
+        <v>0.7111</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4251</v>
+        <v>0.4222</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7148</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3646,16 +3646,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>110.03</v>
+        <v>109.58</v>
       </c>
       <c r="C24" t="n">
-        <v>72.61</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>38.12</v>
       </c>
       <c r="E24" t="n">
-        <v>59.82</v>
+        <v>59.64</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -3664,13 +3664,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7009</v>
+        <v>0.7018</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4018</v>
+        <v>0.4036</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7121</v>
+        <v>0.7123</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>289.38</v>
+        <v>289.88</v>
       </c>
       <c r="C25" t="n">
-        <v>267.45</v>
+        <v>267.46</v>
       </c>
       <c r="D25" t="n">
-        <v>252.12</v>
+        <v>252.13</v>
       </c>
       <c r="E25" t="n">
-        <v>57.69</v>
+        <v>58.17</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -3728,13 +3728,13 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7116</v>
+        <v>0.7091</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4231</v>
+        <v>0.4183</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7086</v>
+        <v>0.7078</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1620.36</v>
+        <v>1625.76</v>
       </c>
       <c r="C26" t="n">
-        <v>1439.75</v>
+        <v>1439.86</v>
       </c>
       <c r="D26" t="n">
-        <v>1178.49</v>
+        <v>1178.52</v>
       </c>
       <c r="E26" t="n">
-        <v>63.63</v>
+        <v>64.16</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -3792,13 +3792,13 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6819</v>
+        <v>0.6792</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3637</v>
+        <v>0.3584</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7075</v>
+        <v>0.7066</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>126.25</v>
+        <v>127.75</v>
       </c>
       <c r="C27" t="n">
-        <v>85.2</v>
+        <v>85.23</v>
       </c>
       <c r="D27" t="n">
-        <v>62.46</v>
+        <v>62.47</v>
       </c>
       <c r="E27" t="n">
-        <v>67.84</v>
+        <v>68.56</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -3856,13 +3856,13 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6572</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3216</v>
+        <v>0.3144</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7063</v>
+        <v>0.7052</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3902,16 +3902,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>206.62</v>
+        <v>208.49</v>
       </c>
       <c r="C28" t="n">
-        <v>139.86</v>
+        <v>139.89</v>
       </c>
       <c r="D28" t="n">
-        <v>96.48</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>68.54000000000001</v>
+        <v>69.11</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -3920,13 +3920,13 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6573</v>
+        <v>0.6544</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3146</v>
+        <v>0.3089</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7052</v>
+        <v>0.7043</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16.66</v>
+        <v>16.67</v>
       </c>
       <c r="C29" t="n">
         <v>12.65</v>
@@ -3975,7 +3975,7 @@
         <v>9.59</v>
       </c>
       <c r="E29" t="n">
-        <v>70.77</v>
+        <v>70.84</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -3984,13 +3984,13 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6462</v>
+        <v>0.6458</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2923</v>
+        <v>0.2916</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7036</v>
+        <v>0.7035</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4030,16 +4030,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1990.49</v>
+        <v>1998.5</v>
       </c>
       <c r="C30" t="n">
-        <v>1701.82</v>
+        <v>1701.98</v>
       </c>
       <c r="D30" t="n">
-        <v>1330.44</v>
+        <v>1330.48</v>
       </c>
       <c r="E30" t="n">
-        <v>66.63</v>
+        <v>66.97</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -4048,13 +4048,13 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.6652</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3337</v>
+        <v>0.3303</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7035</v>
+        <v>0.703</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4094,16 +4094,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37.35</v>
+        <v>37.4</v>
       </c>
       <c r="C31" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="D31" t="n">
-        <v>23.05</v>
+        <v>23.06</v>
       </c>
       <c r="E31" t="n">
-        <v>68.31999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -4112,13 +4112,13 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6584</v>
+        <v>0.6576</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3168</v>
+        <v>0.3152</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7019</v>
+        <v>0.7016</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4158,16 +4158,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>890.6</v>
+        <v>894.84</v>
       </c>
       <c r="C32" t="n">
-        <v>528.26</v>
+        <v>528.35</v>
       </c>
       <c r="D32" t="n">
-        <v>326.3</v>
+        <v>326.33</v>
       </c>
       <c r="E32" t="n">
-        <v>70.38</v>
+        <v>70.59</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -4176,13 +4176,13 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6481</v>
+        <v>0.647</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2962</v>
+        <v>0.2941</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7008</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4222,16 +4222,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>303</v>
+        <v>305.86</v>
       </c>
       <c r="C33" t="n">
-        <v>203.86</v>
+        <v>203.91</v>
       </c>
       <c r="D33" t="n">
-        <v>150.29</v>
+        <v>150.3</v>
       </c>
       <c r="E33" t="n">
-        <v>75.19</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -4240,13 +4240,13 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.624</v>
+        <v>0.622</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2481</v>
+        <v>0.244</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6987</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4286,16 +4286,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>117.27</v>
+        <v>117.51</v>
       </c>
       <c r="C34" t="n">
-        <v>90.56</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="D34" t="n">
         <v>77.52</v>
       </c>
       <c r="E34" t="n">
-        <v>76.31999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -4304,13 +4304,13 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6162</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2368</v>
+        <v>0.2325</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6972</v>
+        <v>0.6966</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4350,16 +4350,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>565.12</v>
+        <v>567.73</v>
       </c>
       <c r="C35" t="n">
-        <v>423.8</v>
+        <v>423.86</v>
       </c>
       <c r="D35" t="n">
-        <v>331.03</v>
+        <v>331.04</v>
       </c>
       <c r="E35" t="n">
-        <v>69.31999999999999</v>
+        <v>69.69</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -4368,13 +4368,13 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6534</v>
+        <v>0.6516</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3068</v>
+        <v>0.3031</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6932</v>
+        <v>0.6926</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4414,16 +4414,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>597.16</v>
+        <v>599.38</v>
       </c>
       <c r="C36" t="n">
-        <v>472.44</v>
+        <v>472.48</v>
       </c>
       <c r="D36" t="n">
-        <v>383.71</v>
+        <v>383.72</v>
       </c>
       <c r="E36" t="n">
-        <v>69.33</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -4432,13 +4432,13 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6534</v>
+        <v>0.6516</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3067</v>
+        <v>0.3032</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6922</v>
+        <v>0.6916</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4478,16 +4478,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>317.05</v>
+        <v>318.12</v>
       </c>
       <c r="C37" t="n">
-        <v>186.08</v>
+        <v>186.1</v>
       </c>
       <c r="D37" t="n">
-        <v>147.97</v>
+        <v>147.98</v>
       </c>
       <c r="E37" t="n">
-        <v>76.31</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -4496,13 +4496,13 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6178</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2369</v>
+        <v>0.2357</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6898</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>316.91</v>
+        <v>319.16</v>
       </c>
       <c r="C38" t="n">
-        <v>177.66</v>
+        <v>177.71</v>
       </c>
       <c r="D38" t="n">
-        <v>171.5</v>
+        <v>171.51</v>
       </c>
       <c r="E38" t="n">
-        <v>77.91</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -4560,13 +4560,13 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6091</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2209</v>
+        <v>0.2182</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6883</v>
+        <v>0.6879</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>748.76</v>
+        <v>749.39</v>
       </c>
       <c r="C39" t="n">
-        <v>698.26</v>
+        <v>698.27</v>
       </c>
       <c r="D39" t="n">
         <v>676.86</v>
       </c>
       <c r="E39" t="n">
-        <v>70.62</v>
+        <v>70.92</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -4624,13 +4624,13 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6469</v>
+        <v>0.6454</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2938</v>
+        <v>0.2908</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6872</v>
+        <v>0.6867</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>727.58</v>
+        <v>728.6799999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>644.71</v>
+        <v>644.73</v>
       </c>
       <c r="D40" t="n">
         <v>614.4</v>
       </c>
       <c r="E40" t="n">
-        <v>73.88</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -4688,13 +4688,13 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6306</v>
+        <v>0.6291</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2612</v>
+        <v>0.2582</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6814</v>
+        <v>0.681</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>309.32</v>
+        <v>309.67</v>
       </c>
       <c r="C41" t="n">
         <v>271.55</v>
@@ -4743,7 +4743,7 @@
         <v>261.54</v>
       </c>
       <c r="E41" t="n">
-        <v>89.22</v>
+        <v>89.34</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -4752,13 +4752,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5533</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1078</v>
+        <v>0.1066</v>
       </c>
       <c r="J41" t="n">
-        <v>0.678</v>
+        <v>0.6778</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -4798,16 +4798,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>224.81</v>
+        <v>224.34</v>
       </c>
       <c r="C42" t="n">
-        <v>146.97</v>
+        <v>146.96</v>
       </c>
       <c r="D42" t="n">
         <v>142.35</v>
       </c>
       <c r="E42" t="n">
-        <v>90.09</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -4816,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5496</v>
+        <v>0.5498</v>
       </c>
       <c r="I42" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0.6754</v>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>134.11</v>
+        <v>134.31</v>
       </c>
       <c r="C43" t="n">
         <v>93.26000000000001</v>
@@ -4871,7 +4871,7 @@
         <v>84.39</v>
       </c>
       <c r="E43" t="n">
-        <v>95.64</v>
+        <v>95.66</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -4880,10 +4880,10 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5218</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0436</v>
+        <v>0.0434</v>
       </c>
       <c r="J43" t="n">
         <v>0.6692</v>
@@ -4926,16 +4926,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>672</v>
+        <v>673.15</v>
       </c>
       <c r="C44" t="n">
-        <v>467.43</v>
+        <v>467.45</v>
       </c>
       <c r="D44" t="n">
-        <v>466.44</v>
+        <v>466.45</v>
       </c>
       <c r="E44" t="n">
-        <v>94.41</v>
+        <v>94.44</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -4944,13 +4944,13 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.528</v>
+        <v>0.5278</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0559</v>
+        <v>0.0556</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6637</v>
+        <v>0.6636</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -4986,20 +4986,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SGE.L</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>876</v>
+        <v>47.29</v>
       </c>
       <c r="C45" t="n">
-        <v>865.48</v>
+        <v>49.11</v>
       </c>
       <c r="D45" t="n">
-        <v>998.4</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>40.51</v>
+        <v>28.16</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -5008,13 +5008,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2974</v>
+        <v>0.3592</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5949</v>
+        <v>0.7184</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4586</v>
+        <v>0.4601</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5044,26 +5044,26 @@
         <v>0.5</v>
       </c>
       <c r="R45" t="n">
-        <v>0.4627</v>
+        <v>0.3487</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>SGE.L</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>242.17</v>
+        <v>876</v>
       </c>
       <c r="C46" t="n">
-        <v>244.75</v>
+        <v>865.48</v>
       </c>
       <c r="D46" t="n">
-        <v>305.31</v>
+        <v>998.4</v>
       </c>
       <c r="E46" t="n">
-        <v>39.9</v>
+        <v>40.51</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -5072,13 +5072,13 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3005</v>
+        <v>0.2974</v>
       </c>
       <c r="I46" t="n">
-        <v>0.601</v>
+        <v>0.5949</v>
       </c>
       <c r="J46" t="n">
-        <v>0.458</v>
+        <v>0.4586</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5108,26 +5108,26 @@
         <v>0.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0.4522</v>
+        <v>0.4627</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>47.71</v>
+        <v>241.43</v>
       </c>
       <c r="C47" t="n">
-        <v>49.12</v>
+        <v>244.73</v>
       </c>
       <c r="D47" t="n">
-        <v>66.23999999999999</v>
+        <v>305.31</v>
       </c>
       <c r="E47" t="n">
-        <v>30.05</v>
+        <v>39.46</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -5136,13 +5136,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3498</v>
+        <v>0.3027</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6995</v>
+        <v>0.6054</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4572</v>
+        <v>0.4586</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>0.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0.3487</v>
+        <v>0.4522</v>
       </c>
     </row>
     <row r="48">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="C48" t="n">
         <v>3.28</v>
@@ -5191,7 +5191,7 @@
         <v>4.3</v>
       </c>
       <c r="E48" t="n">
-        <v>32.17</v>
+        <v>31.49</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -5200,13 +5200,13 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3391</v>
+        <v>0.3426</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6783</v>
+        <v>0.6851</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4556</v>
+        <v>0.4567</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>89.56999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="C49" t="n">
         <v>92.33</v>
@@ -5255,7 +5255,7 @@
         <v>94.75</v>
       </c>
       <c r="E49" t="n">
-        <v>42.03</v>
+        <v>42.46</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -5264,13 +5264,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2898</v>
+        <v>0.2877</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5797</v>
+        <v>0.5754</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4514</v>
+        <v>0.4508</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5306,20 +5306,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>303.43</v>
+        <v>432.61</v>
       </c>
       <c r="C50" t="n">
-        <v>293.51</v>
+        <v>389.16</v>
       </c>
       <c r="D50" t="n">
-        <v>322.99</v>
+        <v>410.58</v>
       </c>
       <c r="E50" t="n">
-        <v>42.33</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -5328,13 +5328,13 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2884</v>
+        <v>0.1773</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5767</v>
+        <v>0.3546</v>
       </c>
       <c r="J50" t="n">
-        <v>0.448</v>
+        <v>0.4481</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>EV_AUTONOMY</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -5361,29 +5361,29 @@
         <v>0.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="R50" t="n">
-        <v>0.4097</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>433.22</v>
+        <v>124.48</v>
       </c>
       <c r="C51" t="n">
-        <v>389.17</v>
+        <v>125.5</v>
       </c>
       <c r="D51" t="n">
-        <v>410.58</v>
+        <v>187.14</v>
       </c>
       <c r="E51" t="n">
-        <v>64.69</v>
+        <v>46.28</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -5392,13 +5392,13 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1765</v>
+        <v>0.2686</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3531</v>
+        <v>0.5372</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4478</v>
+        <v>0.4479</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>EV_AUTONOMY</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -5425,29 +5425,29 @@
         <v>0.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3659</v>
+        <v>0.4487</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>124.97</v>
+        <v>304.6</v>
       </c>
       <c r="C52" t="n">
-        <v>125.51</v>
+        <v>293.53</v>
       </c>
       <c r="D52" t="n">
-        <v>187.15</v>
+        <v>322.99</v>
       </c>
       <c r="E52" t="n">
-        <v>46.67</v>
+        <v>42.95</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -5456,13 +5456,13 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2666</v>
+        <v>0.2852</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5333</v>
+        <v>0.5705</v>
       </c>
       <c r="J52" t="n">
-        <v>0.4473</v>
+        <v>0.447</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>0.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0.4487</v>
+        <v>0.4097</v>
       </c>
     </row>
     <row r="53">
@@ -5502,16 +5502,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53.26</v>
+        <v>53.49</v>
       </c>
       <c r="C53" t="n">
-        <v>54.53</v>
+        <v>54.54</v>
       </c>
       <c r="D53" t="n">
         <v>58.42</v>
       </c>
       <c r="E53" t="n">
-        <v>40.96</v>
+        <v>41.32</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -5520,13 +5520,13 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2952</v>
+        <v>0.2934</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5904</v>
+        <v>0.5868</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4472</v>
+        <v>0.4466</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5562,20 +5562,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>8.300000000000001</v>
+        <v>23.15</v>
       </c>
       <c r="C54" t="n">
-        <v>7.7</v>
+        <v>17.73</v>
       </c>
       <c r="D54" t="n">
-        <v>11.46</v>
+        <v>20.41</v>
       </c>
       <c r="E54" t="n">
-        <v>36.78</v>
+        <v>44.01</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -5584,13 +5584,13 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3161</v>
+        <v>0.28</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6322</v>
+        <v>0.5599</v>
       </c>
       <c r="J54" t="n">
-        <v>0.4455</v>
+        <v>0.4464</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -5620,26 +5620,26 @@
         <v>0.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3377</v>
+        <v>0.4159</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23.39</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>17.73</v>
+        <v>7.7</v>
       </c>
       <c r="D55" t="n">
-        <v>20.41</v>
+        <v>11.46</v>
       </c>
       <c r="E55" t="n">
-        <v>45.43</v>
+        <v>36.89</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -5648,13 +5648,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2729</v>
+        <v>0.3156</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5457</v>
+        <v>0.6311</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4443</v>
+        <v>0.4453</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>0.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4159</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="56">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>74.05</v>
+        <v>73.86</v>
       </c>
       <c r="C56" t="n">
         <v>76.22</v>
       </c>
       <c r="D56" t="n">
-        <v>104.35</v>
+        <v>104.34</v>
       </c>
       <c r="E56" t="n">
-        <v>44.73</v>
+        <v>44.36</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -5712,13 +5712,13 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2764</v>
+        <v>0.2782</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5527</v>
+        <v>0.5564</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4401</v>
+        <v>0.4408</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>21.39</v>
+        <v>21.34</v>
       </c>
       <c r="N56" t="n">
-        <v>0.7861</v>
+        <v>0.7866</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5754,20 +5754,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>413.46</v>
+        <v>11.23</v>
       </c>
       <c r="C57" t="n">
-        <v>399.99</v>
+        <v>10.75</v>
       </c>
       <c r="D57" t="n">
-        <v>457.76</v>
+        <v>12.98</v>
       </c>
       <c r="E57" t="n">
-        <v>52.49</v>
+        <v>55.93</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -5776,13 +5776,13 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2376</v>
+        <v>0.2204</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4751</v>
+        <v>0.4407</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4287</v>
+        <v>0.4279</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5812,26 +5812,26 @@
         <v>0.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0.3825</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11.27</v>
+        <v>40.97</v>
       </c>
       <c r="C58" t="n">
-        <v>10.75</v>
+        <v>37.34</v>
       </c>
       <c r="D58" t="n">
-        <v>12.98</v>
+        <v>42.65</v>
       </c>
       <c r="E58" t="n">
-        <v>56.42</v>
+        <v>56.81</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2179</v>
+        <v>0.2159</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4358</v>
+        <v>0.4319</v>
       </c>
       <c r="J58" t="n">
-        <v>0.4271</v>
+        <v>0.4274</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5876,26 +5876,26 @@
         <v>0.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0.4117</v>
+        <v>0.4173</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>41.04</v>
+        <v>414.77</v>
       </c>
       <c r="C59" t="n">
-        <v>37.34</v>
+        <v>400.01</v>
       </c>
       <c r="D59" t="n">
-        <v>42.65</v>
+        <v>457.76</v>
       </c>
       <c r="E59" t="n">
-        <v>57.06</v>
+        <v>53.67</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -5904,13 +5904,13 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2147</v>
+        <v>0.2316</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4294</v>
+        <v>0.4633</v>
       </c>
       <c r="J59" t="n">
-        <v>0.427</v>
+        <v>0.4269</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>0.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0.4173</v>
+        <v>0.3825</v>
       </c>
     </row>
     <row r="60">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="C60" t="n">
         <v>3.81</v>
@@ -5959,7 +5959,7 @@
         <v>5.32</v>
       </c>
       <c r="E60" t="n">
-        <v>51.24</v>
+        <v>50.82</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -5968,13 +5968,13 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2438</v>
+        <v>0.2459</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4876</v>
+        <v>0.4918</v>
       </c>
       <c r="J60" t="n">
-        <v>0.4238</v>
+        <v>0.4244</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -6010,20 +6010,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENVX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7.13</v>
+        <v>499.05</v>
       </c>
       <c r="C61" t="n">
-        <v>6.06</v>
+        <v>449.1</v>
       </c>
       <c r="D61" t="n">
-        <v>8.050000000000001</v>
+        <v>534.33</v>
       </c>
       <c r="E61" t="n">
-        <v>52.39</v>
+        <v>54.53</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -6032,13 +6032,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.238</v>
+        <v>0.2274</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4761</v>
+        <v>0.4547</v>
       </c>
       <c r="J61" t="n">
-        <v>0.4237</v>
+        <v>0.4244</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6068,26 +6068,26 @@
         <v>0.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0.3489</v>
+        <v>0.3742</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>ENVX</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>81.55</v>
+        <v>7.14</v>
       </c>
       <c r="C62" t="n">
-        <v>61.87</v>
+        <v>6.06</v>
       </c>
       <c r="D62" t="n">
-        <v>65.42</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>62.04</v>
+        <v>52.44</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -6096,13 +6096,13 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1898</v>
+        <v>0.2378</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3796</v>
+        <v>0.4756</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4224</v>
+        <v>0.4237</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6132,26 +6132,26 @@
         <v>0.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0.4363</v>
+        <v>0.3489</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>12.29</v>
+        <v>100.9</v>
       </c>
       <c r="C63" t="n">
-        <v>11.46</v>
+        <v>97.86</v>
       </c>
       <c r="D63" t="n">
-        <v>22.82</v>
+        <v>142.38</v>
       </c>
       <c r="E63" t="n">
-        <v>52.33</v>
+        <v>60.74</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -6160,13 +6160,13 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2384</v>
+        <v>0.1963</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4767</v>
+        <v>0.3926</v>
       </c>
       <c r="J63" t="n">
-        <v>0.4224</v>
+        <v>0.4227</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -6196,26 +6196,26 @@
         <v>0.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0.3394</v>
+        <v>0.4252</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>9.69</v>
+        <v>12.26</v>
       </c>
       <c r="C64" t="n">
-        <v>8.869999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28</v>
+        <v>22.82</v>
       </c>
       <c r="E64" t="n">
-        <v>53.95</v>
+        <v>52.17</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -6224,13 +6224,13 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2302</v>
+        <v>0.2391</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4605</v>
+        <v>0.4783</v>
       </c>
       <c r="J64" t="n">
-        <v>0.4217</v>
+        <v>0.4226</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6260,26 +6260,26 @@
         <v>0.5</v>
       </c>
       <c r="R64" t="n">
-        <v>0.351</v>
+        <v>0.3394</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>508.21</v>
+        <v>9.65</v>
       </c>
       <c r="C65" t="n">
-        <v>449.28</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>534.38</v>
+        <v>13.28</v>
       </c>
       <c r="E65" t="n">
-        <v>56.27</v>
+        <v>53.44</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
@@ -6288,13 +6288,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2186</v>
+        <v>0.2328</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4373</v>
+        <v>0.4656</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4217</v>
+        <v>0.4225</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6324,26 +6324,26 @@
         <v>0.5</v>
       </c>
       <c r="R65" t="n">
-        <v>0.3742</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>101.43</v>
+        <v>82.36</v>
       </c>
       <c r="C66" t="n">
-        <v>97.87</v>
+        <v>61.89</v>
       </c>
       <c r="D66" t="n">
-        <v>142.39</v>
+        <v>65.42</v>
       </c>
       <c r="E66" t="n">
-        <v>61.53</v>
+        <v>63.42</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -6352,13 +6352,13 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1924</v>
+        <v>0.1829</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3847</v>
+        <v>0.3658</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4215</v>
+        <v>0.4203</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>0.5</v>
       </c>
       <c r="R66" t="n">
-        <v>0.4252</v>
+        <v>0.4363</v>
       </c>
     </row>
     <row r="67">
@@ -6398,16 +6398,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>102.88</v>
+        <v>102.75</v>
       </c>
       <c r="C67" t="n">
-        <v>89.95999999999999</v>
+        <v>89.95</v>
       </c>
       <c r="D67" t="n">
         <v>119.41</v>
       </c>
       <c r="E67" t="n">
-        <v>67.73</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -6416,13 +6416,13 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1614</v>
+        <v>0.162</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3227</v>
+        <v>0.324</v>
       </c>
       <c r="J67" t="n">
-        <v>0.4196</v>
+        <v>0.4197</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6462,16 +6462,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>191.03</v>
+        <v>191.27</v>
       </c>
       <c r="C68" t="n">
-        <v>167.75</v>
+        <v>167.76</v>
       </c>
       <c r="D68" t="n">
         <v>206.63</v>
       </c>
       <c r="E68" t="n">
-        <v>55.23</v>
+        <v>55.47</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -6480,13 +6480,13 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2238</v>
+        <v>0.2226</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4477</v>
+        <v>0.4453</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4177</v>
+        <v>0.4173</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>77.34999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="C69" t="n">
         <v>73.92</v>
@@ -6535,7 +6535,7 @@
         <v>77.94</v>
       </c>
       <c r="E69" t="n">
-        <v>52.28</v>
+        <v>51.56</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -6544,13 +6544,13 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2386</v>
+        <v>0.2422</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4772</v>
+        <v>0.4844</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4143</v>
+        <v>0.4153</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>309.39</v>
+        <v>304.25</v>
       </c>
       <c r="C70" t="n">
-        <v>269.5</v>
+        <v>269.4</v>
       </c>
       <c r="D70" t="n">
-        <v>322.8</v>
+        <v>322.77</v>
       </c>
       <c r="E70" t="n">
-        <v>65.88</v>
+        <v>63.46</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -6608,13 +6608,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1706</v>
+        <v>0.1827</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3412</v>
+        <v>0.3654</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4113</v>
+        <v>0.4149</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6654,16 +6654,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>609.21</v>
+        <v>609.62</v>
       </c>
       <c r="C71" t="n">
-        <v>617.72</v>
+        <v>617.73</v>
       </c>
       <c r="D71" t="n">
-        <v>667.89</v>
+        <v>667.9</v>
       </c>
       <c r="E71" t="n">
-        <v>52.88</v>
+        <v>53.17</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2356</v>
+        <v>0.2341</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4712</v>
+        <v>0.4683</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4108</v>
+        <v>0.4103</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>14.08</v>
+        <v>14.09</v>
       </c>
       <c r="N71" t="n">
-        <v>0.8592</v>
+        <v>0.8591</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6718,16 +6718,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>250.32</v>
+        <v>250.16</v>
       </c>
       <c r="C72" t="n">
-        <v>236.68</v>
+        <v>236.67</v>
       </c>
       <c r="D72" t="n">
         <v>266.6</v>
       </c>
       <c r="E72" t="n">
-        <v>66.98</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -6736,13 +6736,13 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1651</v>
+        <v>0.1659</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3302</v>
+        <v>0.3318</v>
       </c>
       <c r="J72" t="n">
-        <v>0.4099</v>
+        <v>0.4102</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>64.17</v>
+        <v>63.99</v>
       </c>
       <c r="C73" t="n">
         <v>41.58</v>
@@ -6791,7 +6791,7 @@
         <v>47.45</v>
       </c>
       <c r="E73" t="n">
-        <v>67.09999999999999</v>
+        <v>66.98</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -6800,13 +6800,13 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1645</v>
+        <v>0.1651</v>
       </c>
       <c r="I73" t="n">
-        <v>0.329</v>
+        <v>0.3302</v>
       </c>
       <c r="J73" t="n">
-        <v>0.4015</v>
+        <v>0.4017</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6842,20 +6842,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>37.38</v>
+        <v>380.67</v>
       </c>
       <c r="C74" t="n">
-        <v>28.04</v>
+        <v>317.02</v>
       </c>
       <c r="D74" t="n">
-        <v>36.04</v>
+        <v>322.74</v>
       </c>
       <c r="E74" t="n">
-        <v>70.48999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1476</v>
+        <v>0.1647</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2951</v>
+        <v>0.3293</v>
       </c>
       <c r="J74" t="n">
-        <v>0.3992</v>
+        <v>0.3986</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6900,26 +6900,26 @@
         <v>0.5</v>
       </c>
       <c r="R74" t="n">
-        <v>0.366</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>380.49</v>
+        <v>37.67</v>
       </c>
       <c r="C75" t="n">
-        <v>317.02</v>
+        <v>28.04</v>
       </c>
       <c r="D75" t="n">
-        <v>322.74</v>
+        <v>36.04</v>
       </c>
       <c r="E75" t="n">
-        <v>67</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
@@ -6928,13 +6928,13 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.165</v>
+        <v>0.1458</v>
       </c>
       <c r="I75" t="n">
-        <v>0.33</v>
+        <v>0.2915</v>
       </c>
       <c r="J75" t="n">
-        <v>0.3987</v>
+        <v>0.3986</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>0.5</v>
       </c>
       <c r="R75" t="n">
-        <v>0.3282</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="76">
@@ -6974,16 +6974,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>95.90000000000001</v>
+        <v>96.86</v>
       </c>
       <c r="C76" t="n">
-        <v>54.65</v>
+        <v>54.67</v>
       </c>
       <c r="D76" t="n">
         <v>56.84</v>
       </c>
       <c r="E76" t="n">
-        <v>74.70999999999999</v>
+        <v>74.95</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1264</v>
+        <v>0.1252</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2529</v>
+        <v>0.2505</v>
       </c>
       <c r="J76" t="n">
-        <v>0.3982</v>
+        <v>0.3978</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -7038,16 +7038,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18.55</v>
+        <v>18.62</v>
       </c>
       <c r="C77" t="n">
         <v>14.73</v>
       </c>
       <c r="D77" t="n">
-        <v>15.6</v>
+        <v>15.61</v>
       </c>
       <c r="E77" t="n">
-        <v>73.31</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -7056,13 +7056,13 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1335</v>
+        <v>0.129</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2669</v>
+        <v>0.2579</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3982</v>
+        <v>0.3969</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>533.26</v>
+        <v>533.4299999999999</v>
       </c>
       <c r="C78" t="n">
         <v>456.85</v>
@@ -7111,7 +7111,7 @@
         <v>470.92</v>
       </c>
       <c r="E78" t="n">
-        <v>69.84999999999999</v>
+        <v>69.92</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -7120,13 +7120,13 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1508</v>
+        <v>0.1504</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3015</v>
+        <v>0.3008</v>
       </c>
       <c r="J78" t="n">
-        <v>0.3934</v>
+        <v>0.3933</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -7166,16 +7166,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>189.88</v>
+        <v>189.04</v>
       </c>
       <c r="C79" t="n">
-        <v>145.08</v>
+        <v>145.06</v>
       </c>
       <c r="D79" t="n">
-        <v>223.67</v>
+        <v>223.66</v>
       </c>
       <c r="E79" t="n">
-        <v>82.22</v>
+        <v>82.02</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -7184,13 +7184,13 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1778</v>
+        <v>0.1798</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3871</v>
+        <v>0.3874</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>93.92</v>
+        <v>94</v>
       </c>
       <c r="C80" t="n">
         <v>64.04000000000001</v>
@@ -7239,7 +7239,7 @@
         <v>71.93000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>77.09</v>
+        <v>77.14</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -7248,10 +7248,10 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1145</v>
+        <v>0.1143</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2291</v>
+        <v>0.2286</v>
       </c>
       <c r="J80" t="n">
         <v>0.387</v>
@@ -7294,16 +7294,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>178.74</v>
+        <v>178.52</v>
       </c>
       <c r="C81" t="n">
-        <v>153.05</v>
+        <v>153.04</v>
       </c>
       <c r="D81" t="n">
-        <v>202.58</v>
+        <v>202.57</v>
       </c>
       <c r="E81" t="n">
-        <v>82.68000000000001</v>
+        <v>82.62</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -7312,13 +7312,13 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0866</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1732</v>
+        <v>0.1738</v>
       </c>
       <c r="J81" t="n">
-        <v>0.3834</v>
+        <v>0.3835</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7358,16 +7358,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>256.28</v>
+        <v>257.55</v>
       </c>
       <c r="C82" t="n">
-        <v>185.76</v>
+        <v>185.79</v>
       </c>
       <c r="D82" t="n">
-        <v>188.02</v>
+        <v>188.03</v>
       </c>
       <c r="E82" t="n">
-        <v>87.52</v>
+        <v>88.7</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -7376,13 +7376,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0624</v>
+        <v>0.0565</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1248</v>
+        <v>0.113</v>
       </c>
       <c r="J82" t="n">
-        <v>0.378</v>
+        <v>0.3762</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>107</v>
+        <v>106.54</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8119</v>
+        <v>0.8126</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -7502,10 +7502,10 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>35.82</v>
+        <v>35.42</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8722</v>
+        <v>0.8728</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.05</v>
+        <v>12.11</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7778</v>
+        <v>0.7776</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -7539,10 +7539,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>35.82</v>
+        <v>35.95</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7123</v>
+        <v>0.7119</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -7562,10 +7562,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>213.55</v>
+        <v>213.63</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7755</v>
+        <v>0.7753</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7576,10 +7576,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>62.69</v>
+        <v>62.77</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7703</v>
+        <v>0.7696</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>496.65</v>
+        <v>498.42</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7534</v>
+        <v>0.7531</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -7613,10 +7613,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>76.66</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7703</v>
+        <v>0.7696</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>262.3</v>
+        <v>262.83</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7532</v>
+        <v>0.7526</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>37.62</v>
+        <v>38.06</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>220.11</v>
+        <v>219.68</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7518</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>39.88</v>
+        <v>39.66</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>188.49</v>
+        <v>188.37</v>
       </c>
       <c r="D8" t="n">
-        <v>0.744</v>
+        <v>0.7442</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>42.83</v>
+        <v>42.69</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -7738,7 +7738,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.36</v>
+        <v>159.22</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7421</v>
+        <v>0.7409</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>63.03</v>
+        <v>42.66</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -7775,7 +7775,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7784,10 +7784,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>158.98</v>
+        <v>80.48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7412</v>
+        <v>0.7406</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>42.48</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>326.99</v>
+        <v>327.23</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7405</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>45.25</v>
+        <v>45.32</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>181.19</v>
+        <v>184.18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.739</v>
+        <v>0.7378</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>50.17</v>
+        <v>50.99</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -7886,19 +7886,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OPTICAL_NETWORKING</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>382.13</v>
+        <v>13.39</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7367</v>
+        <v>0.7365</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -7909,10 +7909,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>48.32</v>
+        <v>59.22</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.7119</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7923,19 +7923,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OPTICAL_NETWORKING</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13.39</v>
+        <v>382.81</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7366</v>
+        <v>0.7359</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -7946,10 +7946,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>59.22</v>
+        <v>48.86</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7123</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>405.02</v>
+        <v>404.58</v>
       </c>
       <c r="D15" t="n">
-        <v>0.735</v>
+        <v>0.7352</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>48.4</v>
+        <v>48.24</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>422.18</v>
+        <v>422.67</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7287</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>47.76</v>
+        <v>47.98</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>54.06</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7244</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>55.97</v>
+        <v>56.08</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>383.44</v>
+        <v>384.84</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7198</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>57.19</v>
+        <v>57.51</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1602.72</v>
+        <v>1612.99</v>
       </c>
       <c r="D19" t="n">
-        <v>0.72</v>
+        <v>0.7194</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>60.1</v>
+        <v>60.52</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>217.6</v>
+        <v>219.68</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7192</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>57.82</v>
+        <v>58.48</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>120.96</v>
+        <v>122.49</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7181</v>
+        <v>0.7167</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>60.16</v>
+        <v>61.1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>454.01</v>
+        <v>455.4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7154</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>58.83</v>
+        <v>59.34</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>412.02</v>
+        <v>412.83</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7148</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>57.49</v>
+        <v>57.78</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>110.03</v>
+        <v>109.58</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7121</v>
+        <v>0.7123</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>59.82</v>
+        <v>59.64</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>289.38</v>
+        <v>289.88</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7086</v>
+        <v>0.7078</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>57.69</v>
+        <v>58.17</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -8376,10 +8376,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1620.36</v>
+        <v>1625.76</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7075</v>
+        <v>0.7066</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>63.63</v>
+        <v>64.16</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>126.25</v>
+        <v>127.75</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7063</v>
+        <v>0.7052</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>67.84</v>
+        <v>68.56</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>206.62</v>
+        <v>208.49</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7052</v>
+        <v>0.7043</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>68.54000000000001</v>
+        <v>69.11</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.66</v>
+        <v>16.67</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7036</v>
+        <v>0.7035</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>70.77</v>
+        <v>70.84</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1990.49</v>
+        <v>1998.5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7035</v>
+        <v>0.703</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>66.63</v>
+        <v>66.97</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37.35</v>
+        <v>37.4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7019</v>
+        <v>0.7016</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>68.31999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -8598,10 +8598,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>890.6</v>
+        <v>894.84</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7008</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>70.38</v>
+        <v>70.59</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>303</v>
+        <v>305.86</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6987</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>75.19</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>117.25</v>
+        <v>117.51</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6972</v>
+        <v>0.6966</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>76.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>565.12</v>
+        <v>567.73</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6932</v>
+        <v>0.6926</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>69.31999999999999</v>
+        <v>69.69</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>597.16</v>
+        <v>599.38</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6922</v>
+        <v>0.6916</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>69.33</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>316.83</v>
+        <v>318.12</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6898</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>76.28</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -8820,10 +8820,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>316.35</v>
+        <v>319.16</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6884</v>
+        <v>0.6879</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>77.84</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>748.76</v>
+        <v>749.39</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6872</v>
+        <v>0.6867</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>70.62</v>
+        <v>70.92</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>727.58</v>
+        <v>728.6799999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6814</v>
+        <v>0.681</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>73.88</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>309.27</v>
+        <v>309.67</v>
       </c>
       <c r="D41" t="n">
-        <v>0.678</v>
+        <v>0.6778</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>89.20999999999999</v>
+        <v>89.34</v>
       </c>
       <c r="H41" t="n">
         <v>1</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>224.81</v>
+        <v>224.34</v>
       </c>
       <c r="D42" t="n">
         <v>0.6754</v>
@@ -8982,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>90.09</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>134.11</v>
+        <v>134.31</v>
       </c>
       <c r="D43" t="n">
         <v>0.6692</v>
@@ -9019,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>95.64</v>
+        <v>95.66</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>672</v>
+        <v>673.15</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6637</v>
+        <v>0.6636</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>94.41</v>
+        <v>94.44</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -9070,7 +9070,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SGE.L</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>876</v>
+        <v>47.29</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4586</v>
+        <v>0.4601</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>40.51</v>
+        <v>28.16</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>improves diversification</t>
+          <t>potentially oversold, improves diversification</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>SGE.L</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>242.17</v>
+        <v>876</v>
       </c>
       <c r="D46" t="n">
-        <v>0.458</v>
+        <v>0.4586</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -9130,21 +9130,21 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>39.9</v>
+        <v>40.51</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>potentially oversold, improves diversification</t>
+          <t>improves diversification</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>47.71</v>
+        <v>241.43</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4572</v>
+        <v>0.4586</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>30.05</v>
+        <v>39.46</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -9190,10 +9190,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4556</v>
+        <v>0.4567</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>32.17</v>
+        <v>31.49</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>89.56999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4514</v>
+        <v>0.4508</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>42.03</v>
+        <v>42.46</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
@@ -9255,19 +9255,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>EV_AUTONOMY</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>303.43</v>
+        <v>432.61</v>
       </c>
       <c r="D50" t="n">
-        <v>0.448</v>
+        <v>0.4481</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>42.33</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -9292,19 +9292,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EV_AUTONOMY</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>433.22</v>
+        <v>124.48</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4478</v>
+        <v>0.4479</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>64.69</v>
+        <v>46.28</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -9329,7 +9329,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>124.97</v>
+        <v>304.6</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4473</v>
+        <v>0.447</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>46.67</v>
+        <v>42.95</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53.26</v>
+        <v>53.49</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4472</v>
+        <v>0.4466</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>40.96</v>
+        <v>41.32</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
@@ -9403,7 +9403,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8.300000000000001</v>
+        <v>23.15</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4455</v>
+        <v>0.4464</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -9426,21 +9426,21 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>36.78</v>
+        <v>44.01</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>potentially oversold, improves diversification</t>
+          <t>improves diversification</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>23.39</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4443</v>
+        <v>0.4453</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -9463,14 +9463,14 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>45.43</v>
+        <v>36.89</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>improves diversification</t>
+          <t>potentially oversold, improves diversification</t>
         </is>
       </c>
     </row>
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>74.03</v>
+        <v>73.86</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4402</v>
+        <v>0.4408</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -9500,10 +9500,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>44.69</v>
+        <v>44.36</v>
       </c>
       <c r="H56" t="n">
-        <v>0.786</v>
+        <v>0.7866</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9523,10 +9523,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>413.46</v>
+        <v>11.23</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4287</v>
+        <v>0.4279</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>52.49</v>
+        <v>55.93</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
@@ -9551,7 +9551,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11.27</v>
+        <v>40.97</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4271</v>
+        <v>0.4274</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>56.42</v>
+        <v>56.81</v>
       </c>
       <c r="H58" t="n">
         <v>1</v>
@@ -9588,7 +9588,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9597,10 +9597,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>41.04</v>
+        <v>414.77</v>
       </c>
       <c r="D59" t="n">
-        <v>0.427</v>
+        <v>0.4269</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>57.06</v>
+        <v>53.67</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="D60" t="n">
-        <v>0.424</v>
+        <v>0.4244</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>51.1</v>
+        <v>50.82</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -9662,7 +9662,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENVX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9671,10 +9671,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7.13</v>
+        <v>499.05</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4237</v>
+        <v>0.4244</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>52.39</v>
+        <v>54.53</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -9699,7 +9699,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>ENVX</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>81.55</v>
+        <v>7.14</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4224</v>
+        <v>0.4237</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>62.04</v>
+        <v>52.44</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
@@ -9736,7 +9736,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12.29</v>
+        <v>100.9</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4224</v>
+        <v>0.4227</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>52.33</v>
+        <v>60.74</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -9773,7 +9773,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9782,10 +9782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9.69</v>
+        <v>12.26</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4217</v>
+        <v>0.4226</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>53.95</v>
+        <v>52.17</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
@@ -9810,7 +9810,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>508.21</v>
+        <v>9.65</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4217</v>
+        <v>0.4225</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>56.27</v>
+        <v>53.44</v>
       </c>
       <c r="H65" t="n">
         <v>1</v>
@@ -9847,7 +9847,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>101.43</v>
+        <v>82.36</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4215</v>
+        <v>0.4203</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>61.53</v>
+        <v>63.42</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
@@ -9893,10 +9893,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>102.88</v>
+        <v>102.75</v>
       </c>
       <c r="D67" t="n">
-        <v>0.4196</v>
+        <v>0.4197</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>67.73</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>191.03</v>
+        <v>191.27</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4177</v>
+        <v>0.4173</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>55.23</v>
+        <v>55.47</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -9967,10 +9967,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>77.34</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4143</v>
+        <v>0.4153</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>52.25</v>
+        <v>51.56</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -10004,10 +10004,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>309.39</v>
+        <v>304.25</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4113</v>
+        <v>0.4149</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>65.88</v>
+        <v>63.46</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
@@ -10041,10 +10041,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>609.21</v>
+        <v>609.62</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4108</v>
+        <v>0.4103</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -10055,10 +10055,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>52.88</v>
+        <v>53.17</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8592</v>
+        <v>0.8591</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>250.32</v>
+        <v>250.16</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4099</v>
+        <v>0.4102</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>66.98</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
@@ -10115,10 +10115,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>64.17</v>
+        <v>63.99</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4015</v>
+        <v>0.4017</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>67.09999999999999</v>
+        <v>66.98</v>
       </c>
       <c r="H73" t="n">
         <v>1</v>
@@ -10143,7 +10143,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>37.38</v>
+        <v>380.67</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3992</v>
+        <v>0.3986</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>70.48999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="H74" t="n">
         <v>1</v>
@@ -10180,7 +10180,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>380.49</v>
+        <v>37.67</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3987</v>
+        <v>0.3986</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>67</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
@@ -10226,10 +10226,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>95.90000000000001</v>
+        <v>96.86</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3982</v>
+        <v>0.3978</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>74.70999999999999</v>
+        <v>74.95</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>18.55</v>
+        <v>18.62</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3982</v>
+        <v>0.3969</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>73.31</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
@@ -10300,10 +10300,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>533.26</v>
+        <v>533.4299999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3934</v>
+        <v>0.3933</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>69.84999999999999</v>
+        <v>69.92</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -10337,10 +10337,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>189.88</v>
+        <v>189.04</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3871</v>
+        <v>0.3874</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>82.22</v>
+        <v>82.02</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>93.92</v>
+        <v>94</v>
       </c>
       <c r="D80" t="n">
         <v>0.387</v>
@@ -10388,7 +10388,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>77.09</v>
+        <v>77.14</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>178.74</v>
+        <v>178.52</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3834</v>
+        <v>0.3835</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>82.68000000000001</v>
+        <v>82.62</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -10448,10 +10448,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>256.28</v>
+        <v>257.55</v>
       </c>
       <c r="D82" t="n">
-        <v>0.378</v>
+        <v>0.3762</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>87.52</v>
+        <v>88.7</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
@@ -10561,25 +10561,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.742</v>
+        <v>0.7406</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1219</v>
+        <v>0.1218</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="G2" t="n">
-        <v>5470</v>
+        <v>5460</v>
       </c>
       <c r="H2" t="n">
-        <v>80.37</v>
+        <v>80.48</v>
       </c>
       <c r="I2" t="n">
-        <v>68.06</v>
+        <v>67.84</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6872</v>
+        <v>0.6867</v>
       </c>
       <c r="D3" t="n">
         <v>0.1071</v>
@@ -10622,10 +10622,10 @@
         <v>5150</v>
       </c>
       <c r="H3" t="n">
-        <v>748.71</v>
+        <v>749.39</v>
       </c>
       <c r="I3" t="n">
-        <v>6.88</v>
+        <v>6.87</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7086</v>
+        <v>0.7078</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1524</v>
+        <v>0.1526</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -10668,10 +10668,10 @@
         <v>5040</v>
       </c>
       <c r="H4" t="n">
-        <v>289.38</v>
+        <v>289.88</v>
       </c>
       <c r="I4" t="n">
-        <v>17.42</v>
+        <v>17.39</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -10699,10 +10699,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6815</v>
+        <v>0.681</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1446</v>
+        <v>0.1448</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -10714,10 +10714,10 @@
         <v>4890</v>
       </c>
       <c r="H5" t="n">
-        <v>727.46</v>
+        <v>728.64</v>
       </c>
       <c r="I5" t="n">
-        <v>6.72</v>
+        <v>6.71</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -10745,25 +10745,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7533</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2386</v>
+        <v>0.2384</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="G6" t="n">
-        <v>4820</v>
+        <v>4810</v>
       </c>
       <c r="H6" t="n">
-        <v>262.24</v>
+        <v>262.83</v>
       </c>
       <c r="I6" t="n">
-        <v>18.38</v>
+        <v>18.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.678</v>
+        <v>0.6778</v>
       </c>
       <c r="D7" t="n">
         <v>0.1764</v>
@@ -10806,10 +10806,10 @@
         <v>4690</v>
       </c>
       <c r="H7" t="n">
-        <v>309.27</v>
+        <v>309.68</v>
       </c>
       <c r="I7" t="n">
-        <v>15.16</v>
+        <v>15.14</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7367</v>
+        <v>0.7359</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2464</v>
+        <v>0.2465</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10852,10 +10852,10 @@
         <v>4660</v>
       </c>
       <c r="H8" t="n">
-        <v>382.12</v>
+        <v>382.8</v>
       </c>
       <c r="I8" t="n">
-        <v>12.2</v>
+        <v>12.17</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -10883,25 +10883,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.735</v>
+        <v>0.7352</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2495</v>
+        <v>0.2494</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="G9" t="n">
-        <v>4630</v>
+        <v>4640</v>
       </c>
       <c r="H9" t="n">
-        <v>405.05</v>
+        <v>404.66</v>
       </c>
       <c r="I9" t="n">
-        <v>11.43</v>
+        <v>11.47</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -10929,25 +10929,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2603</v>
+        <v>0.2604</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="G10" t="n">
-        <v>4450</v>
+        <v>4440</v>
       </c>
       <c r="H10" t="n">
-        <v>454.01</v>
+        <v>455.4</v>
       </c>
       <c r="I10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -10975,25 +10975,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6972</v>
+        <v>0.6966</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2516</v>
+        <v>0.2515</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="G11" t="n">
-        <v>4390</v>
+        <v>4380</v>
       </c>
       <c r="H11" t="n">
-        <v>117.25</v>
+        <v>117.49</v>
       </c>
       <c r="I11" t="n">
-        <v>37.44</v>
+        <v>37.28</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6922</v>
+        <v>0.6917</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2472</v>
+        <v>0.2477</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -11036,10 +11036,10 @@
         <v>4370</v>
       </c>
       <c r="H12" t="n">
-        <v>596.92</v>
+        <v>599.29</v>
       </c>
       <c r="I12" t="n">
-        <v>7.32</v>
+        <v>7.29</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7148</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2818</v>
+        <v>0.2819</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="G13" t="n">
-        <v>4320</v>
+        <v>4310</v>
       </c>
       <c r="H13" t="n">
-        <v>411.96</v>
+        <v>412.67</v>
       </c>
       <c r="I13" t="n">
-        <v>10.49</v>
+        <v>10.44</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -11113,10 +11113,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6932</v>
+        <v>0.6926</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2725</v>
+        <v>0.2732</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11128,10 +11128,10 @@
         <v>4230</v>
       </c>
       <c r="H14" t="n">
-        <v>564.88</v>
+        <v>567.6799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>7.49</v>
+        <v>7.45</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7075</v>
+        <v>0.7066</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3225</v>
+        <v>0.3224</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11174,10 +11174,10 @@
         <v>4020</v>
       </c>
       <c r="H15" t="n">
-        <v>1620.01</v>
+        <v>1625.75</v>
       </c>
       <c r="I15" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -11220,10 +11220,10 @@
         <v>3970</v>
       </c>
       <c r="H16" t="n">
-        <v>134.12</v>
+        <v>134.38</v>
       </c>
       <c r="I16" t="n">
-        <v>29.6</v>
+        <v>29.54</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7287</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3576</v>
+        <v>0.3577</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -11266,10 +11266,10 @@
         <v>3930</v>
       </c>
       <c r="H17" t="n">
-        <v>422.2</v>
+        <v>422.72</v>
       </c>
       <c r="I17" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -11297,25 +11297,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7412</v>
+        <v>0.7408</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3952</v>
+        <v>0.3953</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="G18" t="n">
-        <v>3770</v>
+        <v>3760</v>
       </c>
       <c r="H18" t="n">
-        <v>158.96</v>
+        <v>159.3</v>
       </c>
       <c r="I18" t="n">
-        <v>23.72</v>
+        <v>23.6</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7753</v>
       </c>
       <c r="D19" t="n">
         <v>0.2532</v>
@@ -11352,16 +11352,16 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="G19" t="n">
-        <v>3750</v>
+        <v>3740</v>
       </c>
       <c r="H19" t="n">
-        <v>213.4</v>
+        <v>213.62</v>
       </c>
       <c r="I19" t="n">
-        <v>17.57</v>
+        <v>17.51</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11389,10 +11389,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7035</v>
+        <v>0.7442</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3761</v>
+        <v>0.4091</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11404,10 +11404,10 @@
         <v>3690</v>
       </c>
       <c r="H20" t="n">
-        <v>1990.49</v>
+        <v>188.37</v>
       </c>
       <c r="I20" t="n">
-        <v>1.85</v>
+        <v>19.59</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11435,25 +11435,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.744</v>
+        <v>0.703</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4091</v>
+        <v>0.3765</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="G21" t="n">
-        <v>3690</v>
+        <v>3680</v>
       </c>
       <c r="H21" t="n">
-        <v>188.49</v>
+        <v>1998.5</v>
       </c>
       <c r="I21" t="n">
-        <v>19.58</v>
+        <v>1.84</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -11481,25 +11481,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7063</v>
+        <v>0.7052</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3943</v>
+        <v>0.3964</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="G22" t="n">
-        <v>3590</v>
+        <v>3570</v>
       </c>
       <c r="H22" t="n">
-        <v>126.22</v>
+        <v>127.76</v>
       </c>
       <c r="I22" t="n">
-        <v>28.44</v>
+        <v>27.94</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7405</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="D23" t="n">
         <v>0.4362</v>
@@ -11542,10 +11542,10 @@
         <v>3510</v>
       </c>
       <c r="H23" t="n">
-        <v>327.03</v>
+        <v>327.33</v>
       </c>
       <c r="I23" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -11573,25 +11573,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6987</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4309</v>
+        <v>0.4313</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="G24" t="n">
-        <v>3340</v>
+        <v>3330</v>
       </c>
       <c r="H24" t="n">
-        <v>303.18</v>
+        <v>305.87</v>
       </c>
       <c r="I24" t="n">
-        <v>11.02</v>
+        <v>10.89</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -11619,25 +11619,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7052</v>
+        <v>0.7043</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4396</v>
+        <v>0.4406</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="G25" t="n">
-        <v>3320</v>
+        <v>3310</v>
       </c>
       <c r="H25" t="n">
-        <v>206.54</v>
+        <v>208.67</v>
       </c>
       <c r="I25" t="n">
-        <v>16.07</v>
+        <v>15.86</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6637</v>
+        <v>0.6636</v>
       </c>
       <c r="D26" t="n">
         <v>0.4085</v>
@@ -11674,16 +11674,16 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="G26" t="n">
-        <v>3300</v>
+        <v>3290</v>
       </c>
       <c r="H26" t="n">
-        <v>671.64</v>
+        <v>673.15</v>
       </c>
       <c r="I26" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7513</v>
+        <v>0.7518</v>
       </c>
       <c r="D27" t="n">
-        <v>0.487</v>
+        <v>0.4869</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -11726,10 +11726,10 @@
         <v>3240</v>
       </c>
       <c r="H27" t="n">
-        <v>220.35</v>
+        <v>219.68</v>
       </c>
       <c r="I27" t="n">
-        <v>14.7</v>
+        <v>14.75</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>bullish trend, improves diversification</t>
+          <t>bullish trend, potentially oversold, improves diversification</t>
         </is>
       </c>
     </row>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7204</v>
+        <v>0.7198</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4869</v>
+        <v>0.4874</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -11772,10 +11772,10 @@
         <v>3100</v>
       </c>
       <c r="H28" t="n">
-        <v>383.29</v>
+        <v>384.84</v>
       </c>
       <c r="I28" t="n">
-        <v>8.09</v>
+        <v>8.06</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7019</v>
+        <v>0.7016</v>
       </c>
       <c r="D29" t="n">
         <v>0.4868</v>
@@ -11812,16 +11812,16 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="G29" t="n">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="H29" t="n">
-        <v>37.35</v>
+        <v>37.4</v>
       </c>
       <c r="I29" t="n">
-        <v>81.12</v>
+        <v>80.75</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -11849,25 +11849,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6898</v>
       </c>
       <c r="D30" t="n">
-        <v>0.505</v>
+        <v>0.5052</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="G30" t="n">
-        <v>2870</v>
+        <v>2860</v>
       </c>
       <c r="H30" t="n">
-        <v>316.83</v>
+        <v>318.03</v>
       </c>
       <c r="I30" t="n">
-        <v>9.06</v>
+        <v>8.99</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -11895,25 +11895,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5349</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="G31" t="n">
-        <v>2810</v>
+        <v>2800</v>
       </c>
       <c r="H31" t="n">
-        <v>120.85</v>
+        <v>122.47</v>
       </c>
       <c r="I31" t="n">
-        <v>23.25</v>
+        <v>22.86</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -11941,25 +11941,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.7012</v>
+        <v>0.7008</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5423</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="G32" t="n">
-        <v>2700</v>
+        <v>2690</v>
       </c>
       <c r="H32" t="n">
-        <v>889.7</v>
+        <v>894.6900000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -12002,10 +12002,10 @@
         <v>2600</v>
       </c>
       <c r="H33" t="n">
-        <v>224.81</v>
+        <v>224.34</v>
       </c>
       <c r="I33" t="n">
-        <v>11.57</v>
+        <v>11.59</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -12033,25 +12033,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7245</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5929</v>
+        <v>0.593</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="G34" t="n">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="H34" t="n">
-        <v>53.99</v>
+        <v>54.04</v>
       </c>
       <c r="I34" t="n">
-        <v>45.93</v>
+        <v>45.71</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -12079,13 +12079,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.8119</v>
+        <v>0.8126</v>
       </c>
       <c r="D35" t="n">
         <v>0.6681</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1984</v>
+        <v>0.1981</v>
       </c>
       <c r="F35" t="n">
         <v>2.26</v>
@@ -12094,10 +12094,10 @@
         <v>2260</v>
       </c>
       <c r="H35" t="n">
-        <v>107</v>
+        <v>106.55</v>
       </c>
       <c r="I35" t="n">
-        <v>21.12</v>
+        <v>21.21</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -12125,10 +12125,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.7202</v>
+        <v>0.7195</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6506</v>
+        <v>0.6512</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -12140,10 +12140,10 @@
         <v>2110</v>
       </c>
       <c r="H36" t="n">
-        <v>1600.15</v>
+        <v>1612.2</v>
       </c>
       <c r="I36" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -12171,13 +12171,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.7534</v>
+        <v>0.7531</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4743</v>
+        <v>0.4746</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2623</v>
+        <v>0.2626</v>
       </c>
       <c r="F37" t="n">
         <v>1.89</v>
@@ -12186,10 +12186,10 @@
         <v>1890</v>
       </c>
       <c r="H37" t="n">
-        <v>496.65</v>
+        <v>498.34</v>
       </c>
       <c r="I37" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4515</v>
+        <v>0.4507</v>
       </c>
       <c r="D38" t="n">
         <v>0.2222</v>
@@ -12226,16 +12226,16 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G38" t="n">
-        <v>1690</v>
+        <v>1680</v>
       </c>
       <c r="H38" t="n">
-        <v>89.54000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>18.87</v>
+        <v>18.72</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.7192</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="D39" t="n">
         <v>0.7389</v>
@@ -12272,16 +12272,16 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G39" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="H39" t="n">
-        <v>217.6</v>
+        <v>219.62</v>
       </c>
       <c r="I39" t="n">
-        <v>7.26</v>
+        <v>7.15</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -12309,10 +12309,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.6884</v>
+        <v>0.6879</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7352</v>
+        <v>0.7355</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>1530</v>
       </c>
       <c r="H40" t="n">
-        <v>316.35</v>
+        <v>319.2</v>
       </c>
       <c r="I40" t="n">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.4285</v>
+        <v>0.4268</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2843</v>
+        <v>0.2842</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -12416,10 +12416,10 @@
         <v>1470</v>
       </c>
       <c r="H42" t="n">
-        <v>413.53</v>
+        <v>414.83</v>
       </c>
       <c r="I42" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -12447,10 +12447,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.4479</v>
+        <v>0.4481</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3415</v>
+        <v>0.3414</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>1420</v>
       </c>
       <c r="H43" t="n">
-        <v>433.05</v>
+        <v>432.45</v>
       </c>
       <c r="I43" t="n">
         <v>3.28</v>
@@ -12493,10 +12493,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4143</v>
+        <v>0.4155</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2972</v>
+        <v>0.2971</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -12508,10 +12508,10 @@
         <v>1400</v>
       </c>
       <c r="H44" t="n">
-        <v>77.34</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>18.1</v>
+        <v>18.17</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.458</v>
+        <v>0.4586</v>
       </c>
       <c r="D45" t="n">
         <v>0.3715</v>
@@ -12554,10 +12554,10 @@
         <v>1380</v>
       </c>
       <c r="H45" t="n">
-        <v>242.17</v>
+        <v>241.4</v>
       </c>
       <c r="I45" t="n">
-        <v>5.7</v>
+        <v>5.72</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -12585,10 +12585,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.7036</v>
+        <v>0.7035</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7681</v>
+        <v>0.768</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -12600,10 +12600,10 @@
         <v>1370</v>
       </c>
       <c r="H46" t="n">
-        <v>16.66</v>
+        <v>16.68</v>
       </c>
       <c r="I46" t="n">
-        <v>82.23</v>
+        <v>82.13</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -12631,25 +12631,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.4224</v>
+        <v>0.4202</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3504</v>
+        <v>0.3502</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G47" t="n">
-        <v>1320</v>
+        <v>1310</v>
       </c>
       <c r="H47" t="n">
-        <v>81.54000000000001</v>
+        <v>82.41</v>
       </c>
       <c r="I47" t="n">
-        <v>16.19</v>
+        <v>15.9</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -12677,10 +12677,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.7121</v>
+        <v>0.7123</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7833</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -12692,10 +12692,10 @@
         <v>1300</v>
       </c>
       <c r="H48" t="n">
-        <v>110.03</v>
+        <v>109.58</v>
       </c>
       <c r="I48" t="n">
-        <v>11.81</v>
+        <v>11.86</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.427</v>
+        <v>0.4274</v>
       </c>
       <c r="D49" t="n">
         <v>0.3769</v>
@@ -12738,10 +12738,10 @@
         <v>1280</v>
       </c>
       <c r="H49" t="n">
-        <v>41.04</v>
+        <v>40.97</v>
       </c>
       <c r="I49" t="n">
-        <v>31.19</v>
+        <v>31.24</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.4099</v>
+        <v>0.4102</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3654</v>
+        <v>0.3655</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -12784,10 +12784,10 @@
         <v>1250</v>
       </c>
       <c r="H50" t="n">
-        <v>250.32</v>
+        <v>250.1</v>
       </c>
       <c r="I50" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -12815,10 +12815,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.448</v>
+        <v>0.4469</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4307</v>
+        <v>0.4311</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -12830,10 +12830,10 @@
         <v>1220</v>
       </c>
       <c r="H51" t="n">
-        <v>303.32</v>
+        <v>304.77</v>
       </c>
       <c r="I51" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -12861,10 +12861,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.4474</v>
+        <v>0.4479</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4919</v>
+        <v>0.4921</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -12876,10 +12876,10 @@
         <v>1090</v>
       </c>
       <c r="H52" t="n">
-        <v>124.9</v>
+        <v>124.48</v>
       </c>
       <c r="I52" t="n">
-        <v>8.73</v>
+        <v>8.76</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.4176</v>
+        <v>0.4173</v>
       </c>
       <c r="D53" t="n">
         <v>0.4652</v>
@@ -12922,10 +12922,10 @@
         <v>1070</v>
       </c>
       <c r="H53" t="n">
-        <v>191.09</v>
+        <v>191.27</v>
       </c>
       <c r="I53" t="n">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.4554</v>
+        <v>0.4603</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5235</v>
+        <v>0.53</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -12968,10 +12968,10 @@
         <v>1040</v>
       </c>
       <c r="H54" t="n">
-        <v>2.96</v>
+        <v>47.26</v>
       </c>
       <c r="I54" t="n">
-        <v>351.35</v>
+        <v>22.01</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12999,25 +12999,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.4572</v>
+        <v>0.4568</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5305</v>
+        <v>0.5238</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G55" t="n">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="H55" t="n">
-        <v>47.71</v>
+        <v>2.93</v>
       </c>
       <c r="I55" t="n">
-        <v>21.59</v>
+        <v>354.95</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.4196</v>
+        <v>0.4197</v>
       </c>
       <c r="D56" t="n">
         <v>0.5</v>
@@ -13060,10 +13060,10 @@
         <v>1000</v>
       </c>
       <c r="H56" t="n">
-        <v>102.88</v>
+        <v>102.75</v>
       </c>
       <c r="I56" t="n">
-        <v>9.720000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -13091,10 +13091,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.4443</v>
+        <v>0.4464</v>
       </c>
       <c r="D57" t="n">
-        <v>0.5417</v>
+        <v>0.5414</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -13106,10 +13106,10 @@
         <v>980</v>
       </c>
       <c r="H57" t="n">
-        <v>23.39</v>
+        <v>23.15</v>
       </c>
       <c r="I57" t="n">
-        <v>41.9</v>
+        <v>42.33</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -13137,13 +13137,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.4109</v>
+        <v>0.4102</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3287</v>
+        <v>0.3286</v>
       </c>
       <c r="E58" t="n">
-        <v>0.162</v>
+        <v>0.1621</v>
       </c>
       <c r="F58" t="n">
         <v>0.95</v>
@@ -13152,7 +13152,7 @@
         <v>950</v>
       </c>
       <c r="H58" t="n">
-        <v>609.11</v>
+        <v>609.76</v>
       </c>
       <c r="I58" t="n">
         <v>1.56</v>
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.4214</v>
+        <v>0.4226</v>
       </c>
       <c r="D59" t="n">
         <v>0.5538999999999999</v>
@@ -13192,16 +13192,16 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G59" t="n">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="H59" t="n">
-        <v>101.45</v>
+        <v>100.93</v>
       </c>
       <c r="I59" t="n">
-        <v>8.869999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.4472</v>
+        <v>0.4467</v>
       </c>
       <c r="D60" t="n">
         <v>0.6036</v>
@@ -13244,10 +13244,10 @@
         <v>850</v>
       </c>
       <c r="H60" t="n">
-        <v>53.26</v>
+        <v>53.46</v>
       </c>
       <c r="I60" t="n">
-        <v>15.96</v>
+        <v>15.9</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -13275,25 +13275,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.4217</v>
+        <v>0.4225</v>
       </c>
       <c r="D61" t="n">
-        <v>0.5871</v>
+        <v>0.5869</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G61" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="H61" t="n">
-        <v>9.69</v>
+        <v>9.65</v>
       </c>
       <c r="I61" t="n">
-        <v>85.66</v>
+        <v>87.05</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.4273</v>
+        <v>0.4279</v>
       </c>
       <c r="D62" t="n">
-        <v>0.6012</v>
+        <v>0.6011</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -13336,10 +13336,10 @@
         <v>820</v>
       </c>
       <c r="H62" t="n">
-        <v>11.26</v>
+        <v>11.23</v>
       </c>
       <c r="I62" t="n">
-        <v>72.81999999999999</v>
+        <v>73.02</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -13367,25 +13367,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.4113</v>
+        <v>0.4148</v>
       </c>
       <c r="D63" t="n">
-        <v>0.6016</v>
+        <v>0.6029</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G63" t="n">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="H63" t="n">
-        <v>309.39</v>
+        <v>304.35</v>
       </c>
       <c r="I63" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.4456</v>
+        <v>0.4453</v>
       </c>
       <c r="D64" t="n">
         <v>0.6439</v>
@@ -13428,10 +13428,10 @@
         <v>760</v>
       </c>
       <c r="H64" t="n">
-        <v>8.289999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>91.68000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>0.4237</v>
       </c>
       <c r="D65" t="n">
-        <v>0.6407</v>
+        <v>0.6411</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -13474,10 +13474,10 @@
         <v>730</v>
       </c>
       <c r="H65" t="n">
-        <v>7.13</v>
+        <v>7.14</v>
       </c>
       <c r="I65" t="n">
-        <v>102.38</v>
+        <v>102.24</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.4215</v>
+        <v>0.4243</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6524</v>
+        <v>0.6511</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G66" t="n">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="H66" t="n">
-        <v>508.91</v>
+        <v>499.26</v>
       </c>
       <c r="I66" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.424</v>
+        <v>0.4245</v>
       </c>
       <c r="D67" t="n">
         <v>0.6869</v>
@@ -13566,10 +13566,10 @@
         <v>640</v>
       </c>
       <c r="H67" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="I67" t="n">
-        <v>153.11</v>
+        <v>153.48</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -13597,25 +13597,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.7778</v>
+        <v>0.7776</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8845</v>
+        <v>0.8842</v>
       </c>
       <c r="E68" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0973</v>
       </c>
       <c r="F68" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="G68" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="H68" t="n">
-        <v>12.05</v>
+        <v>12.11</v>
       </c>
       <c r="I68" t="n">
-        <v>39.83</v>
+        <v>40.46</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -13643,13 +13643,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.4402</v>
+        <v>0.4408</v>
       </c>
       <c r="D69" t="n">
         <v>0.6025</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2783</v>
+        <v>0.278</v>
       </c>
       <c r="F69" t="n">
         <v>0.48</v>
@@ -13658,10 +13658,10 @@
         <v>480</v>
       </c>
       <c r="H69" t="n">
-        <v>74.03</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>6.48</v>
+        <v>6.5</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.4015</v>
+        <v>0.4017</v>
       </c>
       <c r="D70" t="n">
         <v>0.754</v>
@@ -13704,10 +13704,10 @@
         <v>470</v>
       </c>
       <c r="H70" t="n">
-        <v>64.17</v>
+        <v>63.99</v>
       </c>
       <c r="I70" t="n">
-        <v>7.32</v>
+        <v>7.34</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -13735,10 +13735,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.4225</v>
+        <v>0.4226</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8032</v>
+        <v>0.8031</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -13750,10 +13750,10 @@
         <v>400</v>
       </c>
       <c r="H71" t="n">
-        <v>12.28</v>
+        <v>12.26</v>
       </c>
       <c r="I71" t="n">
-        <v>32.57</v>
+        <v>32.63</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -13781,10 +13781,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.3987</v>
+        <v>0.3986</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3113</v>
+        <v>0.3114</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>330</v>
       </c>
       <c r="H72" t="n">
-        <v>380.52</v>
+        <v>380.67</v>
       </c>
       <c r="I72" t="n">
         <v>0.87</v>
@@ -13827,7 +13827,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.3934</v>
+        <v>0.3932</v>
       </c>
       <c r="D73" t="n">
         <v>0.3523</v>
@@ -13842,7 +13842,7 @@
         <v>300</v>
       </c>
       <c r="H73" t="n">
-        <v>533.26</v>
+        <v>533.55</v>
       </c>
       <c r="I73" t="n">
         <v>0.5600000000000001</v>
@@ -13873,7 +13873,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3983</v>
+        <v>0.397</v>
       </c>
       <c r="D74" t="n">
         <v>0.4031</v>
@@ -13888,10 +13888,10 @@
         <v>290</v>
       </c>
       <c r="H74" t="n">
-        <v>18.55</v>
+        <v>18.61</v>
       </c>
       <c r="I74" t="n">
-        <v>15.63</v>
+        <v>15.58</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -13919,10 +13919,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.378</v>
+        <v>0.3763</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3514</v>
+        <v>0.3512</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -13934,7 +13934,7 @@
         <v>290</v>
       </c>
       <c r="H75" t="n">
-        <v>256.27</v>
+        <v>257.48</v>
       </c>
       <c r="I75" t="n">
         <v>1.13</v>
@@ -13968,7 +13968,7 @@
         <v>0.387</v>
       </c>
       <c r="D76" t="n">
-        <v>0.4743</v>
+        <v>0.4744</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -13980,10 +13980,10 @@
         <v>240</v>
       </c>
       <c r="H76" t="n">
-        <v>93.92</v>
+        <v>94</v>
       </c>
       <c r="I76" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.387</v>
+        <v>0.3874</v>
       </c>
       <c r="D77" t="n">
-        <v>0.5505</v>
+        <v>0.55</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -14026,7 +14026,7 @@
         <v>210</v>
       </c>
       <c r="H77" t="n">
-        <v>189.98</v>
+        <v>188.98</v>
       </c>
       <c r="I77" t="n">
         <v>1.11</v>
@@ -14060,7 +14060,7 @@
         <v>0.3835</v>
       </c>
       <c r="D78" t="n">
-        <v>0.5681</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -14072,7 +14072,7 @@
         <v>200</v>
       </c>
       <c r="H78" t="n">
-        <v>178.67</v>
+        <v>178.56</v>
       </c>
       <c r="I78" t="n">
         <v>1.12</v>
@@ -14103,10 +14103,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.3992</v>
+        <v>0.3987</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6573</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -14118,10 +14118,10 @@
         <v>160</v>
       </c>
       <c r="H79" t="n">
-        <v>37.37</v>
+        <v>37.65</v>
       </c>
       <c r="I79" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -14149,10 +14149,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.739</v>
+        <v>0.7377</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9812</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -14164,10 +14164,10 @@
         <v>120</v>
       </c>
       <c r="H80" t="n">
-        <v>181.19</v>
+        <v>184.35</v>
       </c>
       <c r="I80" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>

--- a/data/exports/prod-portfolio_intelligence.xlsx
+++ b/data/exports/prod-portfolio_intelligence.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="228">
   <si>
     <t>trade_date</t>
   </si>
@@ -509,7 +509,7 @@
     <t>funding_gap</t>
   </si>
   <si>
-    <t>CRITICAL</t>
+    <t>UNDERFUNDED</t>
   </si>
   <si>
     <t>sell_quantity</t>
@@ -536,18 +536,6 @@
     <t>Recommended because of high tax efficiency, unrealised losses available, long holding period.</t>
   </si>
   <si>
-    <t>Recommended because of unrealised losses available, low concentration risk.</t>
-  </si>
-  <si>
-    <t>Recommended because of unrealised losses available.</t>
-  </si>
-  <si>
-    <t>Recommended because of low concentration risk.</t>
-  </si>
-  <si>
-    <t>Recommended because of large unrealised gains, high concentration risk.</t>
-  </si>
-  <si>
     <t>priority</t>
   </si>
   <si>
@@ -617,7 +605,7 @@
     <t>Bullish trend, Technical score 0.86, Portfolio fit 1.00, Favourable macro environment, Potentially oversold, Strong momentum</t>
   </si>
   <si>
-    <t>Bullish trend, Portfolio fit 0.91, Favourable macro environment, Strong momentum</t>
+    <t>Bullish trend, Portfolio fit 0.92, Favourable macro environment, Strong momentum</t>
   </si>
   <si>
     <t>Bullish trend, Technical score 0.84, Portfolio fit 1.00, Favourable macro environment, Potentially oversold, Strong momentum</t>
@@ -656,25 +644,19 @@
     <t>Portfolio fit 0.90</t>
   </si>
   <si>
-    <t>No strong signals</t>
-  </si>
-  <si>
-    <t>Portfolio fit 0.82</t>
+    <t>Portfolio fit 0.80</t>
+  </si>
+  <si>
+    <t>Portfolio fit 0.81</t>
   </si>
   <si>
     <t>decision</t>
   </si>
   <si>
-    <t>RAISE_CASH</t>
-  </si>
-  <si>
     <t>TRIM_POSITIONS</t>
   </si>
   <si>
-    <t>Cash reserve below target</t>
-  </si>
-  <si>
-    <t>Portfolio overdeployed by £7,943.25</t>
+    <t>Portfolio overdeployed by £893.37</t>
   </si>
   <si>
     <t>Metric</t>
@@ -1426,13 +1408,13 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1440,16 +1422,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2">
+        <v>2336.28</v>
+      </c>
+      <c r="E2" t="s">
         <v>175</v>
-      </c>
-      <c r="C2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2">
-        <v>2369.74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1457,16 +1439,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3">
+        <v>2012.68</v>
+      </c>
+      <c r="E3" t="s">
         <v>175</v>
-      </c>
-      <c r="C3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3">
-        <v>2097.02</v>
-      </c>
-      <c r="E3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1474,16 +1456,16 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4">
+        <v>1781.15</v>
+      </c>
+      <c r="E4" t="s">
         <v>175</v>
-      </c>
-      <c r="C4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4">
-        <v>1848.13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1491,16 +1473,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
         <v>176</v>
-      </c>
-      <c r="C5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1508,16 +1490,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D6">
-        <v>5133.99</v>
+        <v>4959.34</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1525,50 +1507,50 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D7">
-        <v>4577.96</v>
+        <v>4848.84</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D8">
-        <v>3794.22</v>
+        <v>3691.22</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D9">
-        <v>3593</v>
+        <v>3604.4</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1589,10 +1571,10 @@
         <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1600,13 +1582,13 @@
         <v>136</v>
       </c>
       <c r="B2">
-        <v>7069.51</v>
+        <v>6806.49</v>
       </c>
       <c r="C2">
-        <v>26.7</v>
+        <v>25.87</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1614,13 +1596,13 @@
         <v>140</v>
       </c>
       <c r="B3">
-        <v>5339.62</v>
+        <v>5167.23</v>
       </c>
       <c r="C3">
-        <v>20.17</v>
+        <v>19.64</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1628,13 +1610,13 @@
         <v>142</v>
       </c>
       <c r="B4">
-        <v>4698.36</v>
+        <v>4961.29</v>
       </c>
       <c r="C4">
-        <v>17.74</v>
+        <v>18.86</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1642,13 +1624,13 @@
         <v>137</v>
       </c>
       <c r="B5">
-        <v>4464.69</v>
+        <v>4569.35</v>
       </c>
       <c r="C5">
-        <v>16.86</v>
+        <v>17.37</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1656,13 +1638,13 @@
         <v>141</v>
       </c>
       <c r="B6">
-        <v>2623.01</v>
+        <v>2588.43</v>
       </c>
       <c r="C6">
-        <v>9.91</v>
+        <v>9.84</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1670,13 +1652,13 @@
         <v>135</v>
       </c>
       <c r="B7">
-        <v>2282.31</v>
+        <v>2218.47</v>
       </c>
       <c r="C7">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="D7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1686,12 +1668,12 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1711,362 +1693,62 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="D2">
-        <v>3507.54</v>
+        <v>893.37</v>
       </c>
       <c r="E2">
-        <v>339.67</v>
+        <v>77.05</v>
       </c>
       <c r="F2">
-        <v>0.9789</v>
+        <v>0.9857</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>1.55</v>
       </c>
       <c r="D3">
-        <v>752.8</v>
+        <v>893.37</v>
       </c>
       <c r="E3">
-        <v>47.49</v>
+        <v>77.05</v>
       </c>
       <c r="F3">
-        <v>0.7107</v>
+        <v>0.9857</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>44</v>
+        <v>1.55</v>
       </c>
       <c r="D4">
-        <v>414.04</v>
+        <v>893.37</v>
       </c>
       <c r="E4">
-        <v>26.12</v>
+        <v>77.05</v>
       </c>
       <c r="F4">
-        <v>0.6988</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>31</v>
-      </c>
-      <c r="D5">
-        <v>2596.87</v>
-      </c>
-      <c r="E5">
-        <v>607.1</v>
-      </c>
-      <c r="F5">
-        <v>0.5853</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>21.54</v>
-      </c>
-      <c r="E6">
-        <v>9.82</v>
-      </c>
-      <c r="F6">
-        <v>0.6673</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>60.4</v>
-      </c>
-      <c r="D7">
-        <v>650.46</v>
-      </c>
-      <c r="E7">
-        <v>310.66</v>
-      </c>
-      <c r="F7">
-        <v>0.8409</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>3507.54</v>
-      </c>
-      <c r="E8">
-        <v>339.67</v>
-      </c>
-      <c r="F8">
-        <v>0.9789</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9">
-        <v>80</v>
-      </c>
-      <c r="D9">
-        <v>752.8</v>
-      </c>
-      <c r="E9">
-        <v>47.49</v>
-      </c>
-      <c r="F9">
-        <v>0.4461</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10">
-        <v>44</v>
-      </c>
-      <c r="D10">
-        <v>414.04</v>
-      </c>
-      <c r="E10">
-        <v>26.12</v>
-      </c>
-      <c r="F10">
-        <v>0.4342</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>31</v>
-      </c>
-      <c r="D11">
-        <v>2596.87</v>
-      </c>
-      <c r="E11">
-        <v>607.1</v>
-      </c>
-      <c r="F11">
-        <v>0.3835</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>21.54</v>
-      </c>
-      <c r="E12">
-        <v>9.82</v>
-      </c>
-      <c r="F12">
-        <v>0.3949</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>60.4</v>
-      </c>
-      <c r="D13">
-        <v>650.46</v>
-      </c>
-      <c r="E13">
-        <v>310.66</v>
-      </c>
-      <c r="F13">
-        <v>0.5821</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
-      <c r="D14">
-        <v>3507.54</v>
-      </c>
-      <c r="E14">
-        <v>339.67</v>
-      </c>
-      <c r="F14">
-        <v>0.8242</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <v>80</v>
-      </c>
-      <c r="D15">
-        <v>752.8</v>
-      </c>
-      <c r="E15">
-        <v>47.49</v>
-      </c>
-      <c r="F15">
-        <v>0.4843</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>44</v>
-      </c>
-      <c r="D16">
-        <v>414.04</v>
-      </c>
-      <c r="E16">
-        <v>26.12</v>
-      </c>
-      <c r="F16">
-        <v>0.4486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17">
-        <v>31</v>
-      </c>
-      <c r="D17">
-        <v>2596.87</v>
-      </c>
-      <c r="E17">
-        <v>607.1</v>
-      </c>
-      <c r="F17">
-        <v>0.489</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>21.54</v>
-      </c>
-      <c r="E18">
-        <v>9.82</v>
-      </c>
-      <c r="F18">
-        <v>0.3949</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>187</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19">
-        <v>60.4</v>
-      </c>
-      <c r="D19">
-        <v>650.46</v>
-      </c>
-      <c r="E19">
-        <v>310.66</v>
-      </c>
-      <c r="F19">
-        <v>0.9038</v>
+        <v>0.8387</v>
       </c>
     </row>
   </sheetData>
@@ -2087,13 +1769,13 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2101,16 +1783,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C2">
-        <v>2369.74</v>
+        <v>2336.28</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2118,16 +1800,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C3">
-        <v>2097.02</v>
+        <v>2012.68</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2135,16 +1817,16 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C4">
-        <v>1848.13</v>
+        <v>1781.15</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2152,16 +1834,16 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C5">
-        <v>5133.99</v>
+        <v>4959.34</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2169,50 +1851,50 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C6">
-        <v>4577.96</v>
+        <v>4848.84</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C7">
-        <v>3794.22</v>
+        <v>3691.22</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C8">
-        <v>3593</v>
+        <v>3604.4</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2223,10 +1905,10 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>1400.66</v>
+        <v>1391.77</v>
       </c>
       <c r="D9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>145</v>
@@ -2240,10 +1922,10 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>1353</v>
+        <v>1347.05</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
         <v>145</v>
@@ -2257,10 +1939,10 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>1331.82</v>
+        <v>1323.37</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
         <v>145</v>
@@ -2274,10 +1956,10 @@
         <v>18</v>
       </c>
       <c r="C12">
-        <v>1307.99</v>
+        <v>1299.69</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E12" t="s">
         <v>145</v>
@@ -2291,10 +1973,10 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>1257.68</v>
+        <v>1249.7</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
         <v>146</v>
@@ -2308,10 +1990,10 @@
         <v>18</v>
       </c>
       <c r="C14">
-        <v>1249.74</v>
+        <v>1239.18</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
         <v>146</v>
@@ -2325,10 +2007,10 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>1178.25</v>
+        <v>1173.4</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E15" t="s">
         <v>145</v>
@@ -2342,10 +2024,10 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>1159.71</v>
+        <v>1144.46</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
         <v>145</v>
@@ -2359,10 +2041,10 @@
         <v>18</v>
       </c>
       <c r="C17">
-        <v>1141.18</v>
+        <v>1133.94</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E17" t="s">
         <v>145</v>
@@ -2376,10 +2058,10 @@
         <v>18</v>
       </c>
       <c r="C18">
-        <v>1130.59</v>
+        <v>1123.41</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
         <v>145</v>
@@ -2397,13 +2079,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2414,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2435,7 +2117,7 @@
         <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D1" t="s">
         <v>48</v>
@@ -2482,7 +2164,7 @@
         <v>0.3742</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2493,16 +2175,16 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>90.26000000000001</v>
+        <v>90.31</v>
       </c>
       <c r="D3">
-        <v>0.7996</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="E3">
         <v>0.7554</v>
       </c>
       <c r="F3">
-        <v>0.9137999999999999</v>
+        <v>0.9157</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2511,7 +2193,7 @@
         <v>0.373</v>
       </c>
       <c r="I3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2540,7 +2222,7 @@
         <v>0.3567</v>
       </c>
       <c r="I4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2569,7 +2251,7 @@
         <v>0.3252</v>
       </c>
       <c r="I5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2598,7 +2280,7 @@
         <v>0.3196</v>
       </c>
       <c r="I6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2627,7 +2309,7 @@
         <v>0.3535</v>
       </c>
       <c r="I7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2656,7 +2338,7 @@
         <v>0.3259</v>
       </c>
       <c r="I8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2685,7 +2367,7 @@
         <v>0.3708</v>
       </c>
       <c r="I9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2714,7 +2396,7 @@
         <v>0.3953</v>
       </c>
       <c r="I10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2743,7 +2425,7 @@
         <v>0.3603</v>
       </c>
       <c r="I11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2772,7 +2454,7 @@
         <v>0.3065</v>
       </c>
       <c r="I12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2801,7 +2483,7 @@
         <v>0.3652</v>
       </c>
       <c r="I13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2830,7 +2512,7 @@
         <v>0.3645</v>
       </c>
       <c r="I14" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2859,7 +2541,7 @@
         <v>0.3692</v>
       </c>
       <c r="I15" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2888,7 +2570,7 @@
         <v>0.3549</v>
       </c>
       <c r="I16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2917,7 +2599,7 @@
         <v>0.3304</v>
       </c>
       <c r="I17" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2946,7 +2628,7 @@
         <v>0.3319</v>
       </c>
       <c r="I18" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2975,7 +2657,7 @@
         <v>0.3441</v>
       </c>
       <c r="I19" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3004,7 +2686,7 @@
         <v>0.3105</v>
       </c>
       <c r="I20" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3033,7 +2715,7 @@
         <v>0.3363</v>
       </c>
       <c r="I21" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -3062,7 +2744,7 @@
         <v>0.3313</v>
       </c>
       <c r="I22" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3091,7 +2773,7 @@
         <v>0.2443</v>
       </c>
       <c r="I23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3120,7 +2802,7 @@
         <v>0.2374</v>
       </c>
       <c r="I24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3131,16 +2813,16 @@
         <v>18</v>
       </c>
       <c r="C25">
-        <v>88.19</v>
+        <v>88.06</v>
       </c>
       <c r="D25">
-        <v>0.789</v>
+        <v>0.7883</v>
       </c>
       <c r="E25">
         <v>0.8081</v>
       </c>
       <c r="F25">
-        <v>0.8314</v>
+        <v>0.8263</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3149,7 +2831,7 @@
         <v>0.4125</v>
       </c>
       <c r="I25" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3160,16 +2842,16 @@
         <v>18</v>
       </c>
       <c r="C26">
-        <v>87.89</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="D26">
-        <v>0.7815</v>
+        <v>0.7808</v>
       </c>
       <c r="E26">
         <v>0.7937</v>
       </c>
       <c r="F26">
-        <v>0.8314</v>
+        <v>0.8263</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3178,7 +2860,7 @@
         <v>0.3915</v>
       </c>
       <c r="I26" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3189,16 +2871,16 @@
         <v>18</v>
       </c>
       <c r="C27">
-        <v>86.40000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="D27">
-        <v>0.7936</v>
+        <v>0.7948</v>
       </c>
       <c r="E27">
         <v>0.7983</v>
       </c>
       <c r="F27">
-        <v>0.733</v>
+        <v>0.7413</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3207,7 +2889,7 @@
         <v>0.2943</v>
       </c>
       <c r="I27" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3236,7 +2918,7 @@
         <v>0.3541</v>
       </c>
       <c r="I28" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3265,7 +2947,7 @@
         <v>0.3567</v>
       </c>
       <c r="I29" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3294,7 +2976,7 @@
         <v>0.3343</v>
       </c>
       <c r="I30" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3323,7 +3005,7 @@
         <v>0.3252</v>
       </c>
       <c r="I31" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3352,7 +3034,7 @@
         <v>0.3135</v>
       </c>
       <c r="I32" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3381,7 +3063,7 @@
         <v>0.3492</v>
       </c>
       <c r="I33" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3410,7 +3092,7 @@
         <v>0.3339</v>
       </c>
       <c r="I34" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3439,7 +3121,7 @@
         <v>0.2904</v>
       </c>
       <c r="I35" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3468,7 +3150,7 @@
         <v>0.3105</v>
       </c>
       <c r="I36" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3497,7 +3179,7 @@
         <v>0.2593</v>
       </c>
       <c r="I37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3526,7 +3208,7 @@
         <v>0.301</v>
       </c>
       <c r="I38" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3555,7 +3237,7 @@
         <v>0.2633</v>
       </c>
       <c r="I39" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3584,7 +3266,7 @@
         <v>0.2665</v>
       </c>
       <c r="I40" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3613,7 +3295,7 @@
         <v>0.3435</v>
       </c>
       <c r="I41" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -3642,7 +3324,7 @@
         <v>0.3086</v>
       </c>
       <c r="I42" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -3671,7 +3353,7 @@
         <v>0.3172</v>
       </c>
       <c r="I43" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3700,7 +3382,7 @@
         <v>0.3264</v>
       </c>
       <c r="I44" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3729,7 +3411,7 @@
         <v>0.312</v>
       </c>
       <c r="I45" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3740,16 +3422,16 @@
         <v>18</v>
       </c>
       <c r="C46">
-        <v>65.31</v>
+        <v>65.53</v>
       </c>
       <c r="D46">
-        <v>0.7662</v>
+        <v>0.7675</v>
       </c>
       <c r="E46">
         <v>0.6943</v>
       </c>
       <c r="F46">
-        <v>0.733</v>
+        <v>0.7413</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -3758,7 +3440,7 @@
         <v>0.3198</v>
       </c>
       <c r="I46" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3787,7 +3469,7 @@
         <v>0.4528</v>
       </c>
       <c r="I47" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3816,7 +3498,7 @@
         <v>0.4643</v>
       </c>
       <c r="I48" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3845,7 +3527,7 @@
         <v>0.3638</v>
       </c>
       <c r="I49" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3874,7 +3556,7 @@
         <v>0.3179</v>
       </c>
       <c r="I50" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3903,7 +3585,7 @@
         <v>0.3353</v>
       </c>
       <c r="I51" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3932,7 +3614,7 @@
         <v>0.5183</v>
       </c>
       <c r="I52" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3961,7 +3643,7 @@
         <v>0.3752</v>
       </c>
       <c r="I53" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3990,7 +3672,7 @@
         <v>0.3429</v>
       </c>
       <c r="I54" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -4019,7 +3701,7 @@
         <v>0.3647</v>
       </c>
       <c r="I55" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -4048,7 +3730,7 @@
         <v>0.3574</v>
       </c>
       <c r="I56" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -4077,7 +3759,7 @@
         <v>0.3292</v>
       </c>
       <c r="I57" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4106,7 +3788,7 @@
         <v>0.5276999999999999</v>
       </c>
       <c r="I58" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4135,7 +3817,7 @@
         <v>0.3444</v>
       </c>
       <c r="I59" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4164,7 +3846,7 @@
         <v>0.3254</v>
       </c>
       <c r="I60" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4193,7 +3875,7 @@
         <v>0.324</v>
       </c>
       <c r="I61" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4222,7 +3904,7 @@
         <v>0.359</v>
       </c>
       <c r="I62" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4251,7 +3933,7 @@
         <v>0.3446</v>
       </c>
       <c r="I63" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4280,7 +3962,7 @@
         <v>0.3585</v>
       </c>
       <c r="I64" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4309,7 +3991,7 @@
         <v>0.3601</v>
       </c>
       <c r="I65" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4338,7 +4020,7 @@
         <v>0.3506</v>
       </c>
       <c r="I66" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4367,7 +4049,7 @@
         <v>0.3484</v>
       </c>
       <c r="I67" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -4396,7 +4078,7 @@
         <v>0.3491</v>
       </c>
       <c r="I68" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -4425,7 +4107,7 @@
         <v>0.3806</v>
       </c>
       <c r="I69" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -4454,7 +4136,7 @@
         <v>0.3303</v>
       </c>
       <c r="I70" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4483,7 +4165,7 @@
         <v>0.3409</v>
       </c>
       <c r="I71" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -4512,7 +4194,7 @@
         <v>0.3839</v>
       </c>
       <c r="I72" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4541,7 +4223,7 @@
         <v>0.3493</v>
       </c>
       <c r="I73" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4570,7 +4252,7 @@
         <v>0.3314</v>
       </c>
       <c r="I74" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -4599,7 +4281,7 @@
         <v>0.3538</v>
       </c>
       <c r="I75" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4628,7 +4310,7 @@
         <v>0.2532</v>
       </c>
       <c r="I76" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -4657,7 +4339,7 @@
         <v>0.4012</v>
       </c>
       <c r="I77" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4686,7 +4368,7 @@
         <v>0.3182</v>
       </c>
       <c r="I78" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4715,7 +4397,7 @@
         <v>0.3708</v>
       </c>
       <c r="I79" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4744,7 +4426,7 @@
         <v>0.3397</v>
       </c>
       <c r="I80" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4773,7 +4455,7 @@
         <v>0.355</v>
       </c>
       <c r="I81" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4802,7 +4484,7 @@
         <v>0.331</v>
       </c>
       <c r="I82" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4813,16 +4495,16 @@
         <v>133</v>
       </c>
       <c r="C83">
-        <v>39.85</v>
+        <v>39.87</v>
       </c>
       <c r="D83">
-        <v>0.4208</v>
+        <v>0.4209</v>
       </c>
       <c r="E83">
         <v>0.2814</v>
       </c>
       <c r="F83">
-        <v>0.9009</v>
+        <v>0.9016</v>
       </c>
       <c r="G83">
         <v>0.25</v>
@@ -4831,7 +4513,7 @@
         <v>0.3419</v>
       </c>
       <c r="I83" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4842,16 +4524,16 @@
         <v>133</v>
       </c>
       <c r="C84">
-        <v>38.44</v>
+        <v>38.58</v>
       </c>
       <c r="D84">
-        <v>0.4368</v>
+        <v>0.4376</v>
       </c>
       <c r="E84">
         <v>0.2638</v>
       </c>
       <c r="F84">
-        <v>0.7983</v>
+        <v>0.8036</v>
       </c>
       <c r="G84">
         <v>0.25</v>
@@ -4860,7 +4542,7 @@
         <v>0.3192</v>
       </c>
       <c r="I84" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4871,16 +4553,16 @@
         <v>133</v>
       </c>
       <c r="C85">
-        <v>38.24</v>
+        <v>37.95</v>
       </c>
       <c r="D85">
-        <v>0.4198</v>
+        <v>0.4181</v>
       </c>
       <c r="E85">
         <v>0.2032</v>
       </c>
       <c r="F85">
-        <v>0.8226</v>
+        <v>0.8114</v>
       </c>
       <c r="G85">
         <v>0.25</v>
@@ -4889,7 +4571,7 @@
         <v>0.3031</v>
       </c>
       <c r="I85" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -4899,40 +4581,29 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4947,23 +4618,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B3">
         <v>12000</v>
@@ -4971,15 +4642,15 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B4">
-        <v>12000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4987,47 +4658,47 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B6">
-        <v>26477.49</v>
+        <v>36311.25</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B7">
-        <v>26477.49</v>
+        <v>26311.25</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -5035,31 +4706,31 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B12">
-        <v>18534.24</v>
+        <v>25417.88</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B13">
-        <v>7943.25</v>
+        <v>893.37</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B14">
-        <v>7943.25</v>
+        <v>893.37</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5075,23 +4746,23 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B17">
-        <v>12000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B18">
-        <v>7943.25</v>
+        <v>893.37</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
@@ -5408,19 +5079,19 @@
         <v>3215.38</v>
       </c>
       <c r="M2">
-        <v>584.5900268554688</v>
+        <v>577.8099975585938</v>
       </c>
       <c r="N2">
-        <v>2623.01</v>
+        <v>2588.43</v>
       </c>
       <c r="O2">
         <v>3167.87</v>
       </c>
       <c r="P2">
-        <v>-544.86</v>
+        <v>-579.4400000000001</v>
       </c>
       <c r="Q2">
-        <v>-17.2</v>
+        <v>-18.29</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -5458,19 +5129,19 @@
         <v>1737.12</v>
       </c>
       <c r="M3">
-        <v>83.76999664306641</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="N3">
-        <v>2756.37</v>
+        <v>2910.62</v>
       </c>
       <c r="O3">
         <v>1711.47</v>
       </c>
       <c r="P3">
-        <v>1044.9</v>
+        <v>1199.15</v>
       </c>
       <c r="Q3">
-        <v>61.05</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -5508,19 +5179,19 @@
         <v>2367.35</v>
       </c>
       <c r="M4">
-        <v>208.1900024414062</v>
+        <v>202.6399993896484</v>
       </c>
       <c r="N4">
-        <v>2802.4</v>
+        <v>2723.31</v>
       </c>
       <c r="O4">
         <v>2332.44</v>
       </c>
       <c r="P4">
-        <v>469.96</v>
+        <v>390.87</v>
       </c>
       <c r="Q4">
-        <v>20.15</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -5558,19 +5229,19 @@
         <v>1887.37</v>
       </c>
       <c r="M5">
-        <v>475.5050048828125</v>
+        <v>455.739990234375</v>
       </c>
       <c r="N5">
-        <v>4267.11</v>
+        <v>4083.18</v>
       </c>
       <c r="O5">
         <v>1859.5</v>
       </c>
       <c r="P5">
-        <v>2407.61</v>
+        <v>2223.68</v>
       </c>
       <c r="Q5">
-        <v>129.48</v>
+        <v>119.58</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -5608,19 +5279,19 @@
         <v>2105.17</v>
       </c>
       <c r="M6">
-        <v>98.44999694824219</v>
+        <v>95.84999847412109</v>
       </c>
       <c r="N6">
-        <v>2282.31</v>
+        <v>2218.47</v>
       </c>
       <c r="O6">
         <v>2074.09</v>
       </c>
       <c r="P6">
-        <v>208.22</v>
+        <v>144.38</v>
       </c>
       <c r="Q6">
-        <v>10.04</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -5658,19 +5329,19 @@
         <v>2018.79</v>
       </c>
       <c r="M7">
-        <v>83.76999664306641</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="N7">
-        <v>1941.99</v>
+        <v>2050.67</v>
       </c>
       <c r="O7">
         <v>1989.77</v>
       </c>
       <c r="P7">
-        <v>-47.78</v>
+        <v>60.9</v>
       </c>
       <c r="Q7">
-        <v>-2.4</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -5708,19 +5379,19 @@
         <v>3079.13</v>
       </c>
       <c r="M8">
-        <v>396.6799926757812</v>
+        <v>384.489990234375</v>
       </c>
       <c r="N8">
-        <v>3263.1</v>
+        <v>3157.75</v>
       </c>
       <c r="O8">
         <v>3033.63</v>
       </c>
       <c r="P8">
-        <v>229.47</v>
+        <v>124.12</v>
       </c>
       <c r="Q8">
-        <v>7.56</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -5758,19 +5429,19 @@
         <v>1847.98</v>
       </c>
       <c r="M9">
-        <v>396.6799926757812</v>
+        <v>384.489990234375</v>
       </c>
       <c r="N9">
-        <v>2076.52</v>
+        <v>2009.48</v>
       </c>
       <c r="O9">
         <v>1820.65</v>
       </c>
       <c r="P9">
-        <v>255.87</v>
+        <v>188.83</v>
       </c>
       <c r="Q9">
-        <v>14.05</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -5808,19 +5479,19 @@
         <v>713.5</v>
       </c>
       <c r="M10">
-        <v>9.409999847412109</v>
+        <v>9.484999656677246</v>
       </c>
       <c r="N10">
-        <v>562.96</v>
+        <v>566.54</v>
       </c>
       <c r="O10">
         <v>705.3099999999999</v>
       </c>
       <c r="P10">
-        <v>-142.35</v>
+        <v>-138.77</v>
       </c>
       <c r="Q10">
-        <v>-20.18</v>
+        <v>-19.68</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -5858,19 +5529,19 @@
         <v>396.11</v>
       </c>
       <c r="M11">
-        <v>9.409999847412109</v>
+        <v>9.484999656677246</v>
       </c>
       <c r="N11">
-        <v>309.63</v>
+        <v>311.59</v>
       </c>
       <c r="O11">
         <v>387.92</v>
       </c>
       <c r="P11">
-        <v>-78.29000000000001</v>
+        <v>-76.33</v>
       </c>
       <c r="Q11">
-        <v>-20.18</v>
+        <v>-19.68</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -5908,19 +5579,19 @@
         <v>2535.49</v>
       </c>
       <c r="M12">
-        <v>10.77000045776367</v>
+        <v>11.08500003814697</v>
       </c>
       <c r="N12">
-        <v>3575.99</v>
+        <v>3674.67</v>
       </c>
       <c r="O12">
         <v>2498.04</v>
       </c>
       <c r="P12">
-        <v>1077.95</v>
+        <v>1176.63</v>
       </c>
       <c r="Q12">
-        <v>43.15</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -5958,19 +5629,19 @@
         <v>11.84</v>
       </c>
       <c r="M13">
-        <v>10.77000045776367</v>
+        <v>11.08500003814697</v>
       </c>
       <c r="N13">
-        <v>16.11</v>
+        <v>16.55</v>
       </c>
       <c r="O13">
         <v>11.72</v>
       </c>
       <c r="P13">
-        <v>4.39</v>
+        <v>4.83</v>
       </c>
       <c r="Q13">
-        <v>37.46</v>
+        <v>41.21</v>
       </c>
     </row>
   </sheetData>
@@ -6068,7 +5739,7 @@
         <v>0.5108</v>
       </c>
       <c r="J2">
-        <v>0.7996</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -6077,10 +5748,10 @@
         <v>135</v>
       </c>
       <c r="M2">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="N2">
-        <v>0.9137999999999999</v>
+        <v>0.9157</v>
       </c>
       <c r="O2" t="s">
         <v>143</v>
@@ -6124,7 +5795,7 @@
         <v>0.5966</v>
       </c>
       <c r="J3">
-        <v>0.7936</v>
+        <v>0.7948</v>
       </c>
       <c r="K3" t="s">
         <v>18</v>
@@ -6133,10 +5804,10 @@
         <v>136</v>
       </c>
       <c r="M3">
-        <v>26.7</v>
+        <v>25.87</v>
       </c>
       <c r="N3">
-        <v>0.733</v>
+        <v>0.7413</v>
       </c>
       <c r="O3" t="s">
         <v>143</v>
@@ -6180,7 +5851,7 @@
         <v>0.6162</v>
       </c>
       <c r="J4">
-        <v>0.789</v>
+        <v>0.7883</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -6189,10 +5860,10 @@
         <v>137</v>
       </c>
       <c r="M4">
-        <v>16.86</v>
+        <v>17.37</v>
       </c>
       <c r="N4">
-        <v>0.8314</v>
+        <v>0.8263</v>
       </c>
       <c r="O4" t="s">
         <v>143</v>
@@ -6236,7 +5907,7 @@
         <v>0.5874</v>
       </c>
       <c r="J5">
-        <v>0.7815</v>
+        <v>0.7808</v>
       </c>
       <c r="K5" t="s">
         <v>18</v>
@@ -6245,10 +5916,10 @@
         <v>137</v>
       </c>
       <c r="M5">
-        <v>16.86</v>
+        <v>17.37</v>
       </c>
       <c r="N5">
-        <v>0.8314</v>
+        <v>0.8263</v>
       </c>
       <c r="O5" t="s">
         <v>143</v>
@@ -6292,7 +5963,7 @@
         <v>0.3887</v>
       </c>
       <c r="J6">
-        <v>0.7662</v>
+        <v>0.7675</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -6301,10 +5972,10 @@
         <v>136</v>
       </c>
       <c r="M6">
-        <v>26.7</v>
+        <v>25.87</v>
       </c>
       <c r="N6">
-        <v>0.733</v>
+        <v>0.7413</v>
       </c>
       <c r="O6" t="s">
         <v>143</v>
@@ -9148,7 +8819,7 @@
         <v>0.5275</v>
       </c>
       <c r="J57">
-        <v>0.4368</v>
+        <v>0.4376</v>
       </c>
       <c r="K57" t="s">
         <v>133</v>
@@ -9157,10 +8828,10 @@
         <v>140</v>
       </c>
       <c r="M57">
-        <v>20.17</v>
+        <v>19.64</v>
       </c>
       <c r="N57">
-        <v>0.7983</v>
+        <v>0.8036</v>
       </c>
       <c r="O57" t="s">
         <v>143</v>
@@ -9876,7 +9547,7 @@
         <v>0.5629</v>
       </c>
       <c r="J70">
-        <v>0.4208</v>
+        <v>0.4209</v>
       </c>
       <c r="K70" t="s">
         <v>133</v>
@@ -9885,10 +9556,10 @@
         <v>141</v>
       </c>
       <c r="M70">
-        <v>9.91</v>
+        <v>9.84</v>
       </c>
       <c r="N70">
-        <v>0.9009</v>
+        <v>0.9016</v>
       </c>
       <c r="O70" t="s">
         <v>143</v>
@@ -9988,7 +9659,7 @@
         <v>0.4064</v>
       </c>
       <c r="J72">
-        <v>0.4198</v>
+        <v>0.4181</v>
       </c>
       <c r="K72" t="s">
         <v>133</v>
@@ -9997,10 +9668,10 @@
         <v>142</v>
       </c>
       <c r="M72">
-        <v>17.74</v>
+        <v>18.86</v>
       </c>
       <c r="N72">
-        <v>0.8226</v>
+        <v>0.8114</v>
       </c>
       <c r="O72" t="s">
         <v>143</v>
@@ -10799,7 +10470,7 @@
         <v>98.44999694824219</v>
       </c>
       <c r="D2">
-        <v>0.7996</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="E2">
         <v>107.6466993713379</v>
@@ -10817,7 +10488,7 @@
         <v>48.91650727527394</v>
       </c>
       <c r="J2">
-        <v>0.9137999999999999</v>
+        <v>0.9157</v>
       </c>
       <c r="K2" t="s">
         <v>145</v>
@@ -10834,7 +10505,7 @@
         <v>208.1900024414062</v>
       </c>
       <c r="D3">
-        <v>0.7936</v>
+        <v>0.7948</v>
       </c>
       <c r="E3">
         <v>204.7893148803711</v>
@@ -10852,7 +10523,7 @@
         <v>40.3439061144787</v>
       </c>
       <c r="J3">
-        <v>0.733</v>
+        <v>0.7413</v>
       </c>
       <c r="K3" t="s">
         <v>145</v>
@@ -10869,7 +10540,7 @@
         <v>9.409999847412109</v>
       </c>
       <c r="D4">
-        <v>0.789</v>
+        <v>0.7883</v>
       </c>
       <c r="E4">
         <v>12.20260008811951</v>
@@ -10887,7 +10558,7 @@
         <v>38.37953061334876</v>
       </c>
       <c r="J4">
-        <v>0.8314</v>
+        <v>0.8263</v>
       </c>
       <c r="K4" t="s">
         <v>146</v>
@@ -10904,7 +10575,7 @@
         <v>10.77000045776367</v>
       </c>
       <c r="D5">
-        <v>0.7815</v>
+        <v>0.7808</v>
       </c>
       <c r="E5">
         <v>10.5473999786377</v>
@@ -10922,7 +10593,7 @@
         <v>41.2614009736754</v>
       </c>
       <c r="J5">
-        <v>0.8314</v>
+        <v>0.8263</v>
       </c>
       <c r="K5" t="s">
         <v>145</v>
@@ -10939,7 +10610,7 @@
         <v>475.5050048828125</v>
       </c>
       <c r="D6">
-        <v>0.7662</v>
+        <v>0.7675</v>
       </c>
       <c r="E6">
         <v>369.9249008178711</v>
@@ -10957,7 +10628,7 @@
         <v>61.13295092708711</v>
       </c>
       <c r="J6">
-        <v>0.733</v>
+        <v>0.7413</v>
       </c>
       <c r="K6" t="s">
         <v>145</v>
@@ -12724,7 +12395,7 @@
         <v>396.6799926757812</v>
       </c>
       <c r="D57">
-        <v>0.4368</v>
+        <v>0.4376</v>
       </c>
       <c r="E57">
         <v>396.7224017333984</v>
@@ -12742,7 +12413,7 @@
         <v>47.24876284391312</v>
       </c>
       <c r="J57">
-        <v>0.7983</v>
+        <v>0.8036</v>
       </c>
       <c r="K57" t="s">
         <v>148</v>
@@ -13179,7 +12850,7 @@
         <v>584.5900268554688</v>
       </c>
       <c r="D70">
-        <v>0.4208</v>
+        <v>0.4209</v>
       </c>
       <c r="E70">
         <v>621.4548010253907</v>
@@ -13197,7 +12868,7 @@
         <v>43.71074795999099</v>
       </c>
       <c r="J70">
-        <v>0.9009</v>
+        <v>0.9016</v>
       </c>
       <c r="K70" t="s">
         <v>148</v>
@@ -13249,7 +12920,7 @@
         <v>83.76999664306641</v>
       </c>
       <c r="D72">
-        <v>0.4198</v>
+        <v>0.4181</v>
       </c>
       <c r="E72">
         <v>78.89790023803711</v>
@@ -13267,7 +12938,7 @@
         <v>59.3609889049034</v>
       </c>
       <c r="J72">
-        <v>0.8226</v>
+        <v>0.8114</v>
       </c>
       <c r="K72" t="s">
         <v>148</v>
@@ -13799,7 +13470,7 @@
         <v>0.7073</v>
       </c>
       <c r="D2">
-        <v>0.1098</v>
+        <v>0.1099</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -13808,7 +13479,7 @@
         <v>5.29</v>
       </c>
       <c r="G2">
-        <v>1400.66</v>
+        <v>1391.77</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -13823,7 +13494,7 @@
         <v>737.0499877929688</v>
       </c>
       <c r="L2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="M2" t="s">
         <v>143</v>
@@ -13835,7 +13506,7 @@
         <v>145</v>
       </c>
       <c r="P2">
-        <v>1400.66</v>
+        <v>1391.77</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -13849,16 +13520,16 @@
         <v>0.7351</v>
       </c>
       <c r="D3">
-        <v>0.1712</v>
+        <v>0.1708</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="G3">
-        <v>1353</v>
+        <v>1347.05</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -13873,7 +13544,7 @@
         <v>290.5499877929688</v>
       </c>
       <c r="L3">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="M3" t="s">
         <v>143</v>
@@ -13885,7 +13556,7 @@
         <v>145</v>
       </c>
       <c r="P3">
-        <v>1353</v>
+        <v>1347.05</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -13899,7 +13570,7 @@
         <v>0.7062</v>
       </c>
       <c r="D4">
-        <v>0.1523</v>
+        <v>0.1524</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -13908,7 +13579,7 @@
         <v>5.03</v>
       </c>
       <c r="G4">
-        <v>1331.82</v>
+        <v>1323.37</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -13923,7 +13594,7 @@
         <v>707.8300170898438</v>
       </c>
       <c r="L4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="s">
         <v>143</v>
@@ -13935,7 +13606,7 @@
         <v>145</v>
       </c>
       <c r="P4">
-        <v>1331.82</v>
+        <v>1323.37</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -13949,7 +13620,7 @@
         <v>0.6954</v>
       </c>
       <c r="D5">
-        <v>0.1549</v>
+        <v>0.1546</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -13958,7 +13629,7 @@
         <v>4.94</v>
       </c>
       <c r="G5">
-        <v>1307.99</v>
+        <v>1299.69</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -13973,7 +13644,7 @@
         <v>285.0199890136719</v>
       </c>
       <c r="L5">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="M5" t="s">
         <v>143</v>
@@ -13985,7 +13656,7 @@
         <v>145</v>
       </c>
       <c r="P5">
-        <v>1307.99</v>
+        <v>1299.69</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -13999,7 +13670,7 @@
         <v>0.7542</v>
       </c>
       <c r="D6">
-        <v>0.2509</v>
+        <v>0.2507</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -14008,7 +13679,7 @@
         <v>4.75</v>
       </c>
       <c r="G6">
-        <v>1257.68</v>
+        <v>1249.7</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -14023,7 +13694,7 @@
         <v>362.2900085449219</v>
       </c>
       <c r="L6">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="M6" t="s">
         <v>143</v>
@@ -14035,7 +13706,7 @@
         <v>146</v>
       </c>
       <c r="P6">
-        <v>1257.68</v>
+        <v>1249.7</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -14049,16 +13720,16 @@
         <v>0.7423999999999999</v>
       </c>
       <c r="D7">
-        <v>0.2442</v>
+        <v>0.2444</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="G7">
-        <v>1249.74</v>
+        <v>1239.18</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -14073,7 +13744,7 @@
         <v>244.1900024414062</v>
       </c>
       <c r="L7">
-        <v>5.12</v>
+        <v>5.07</v>
       </c>
       <c r="M7" t="s">
         <v>143</v>
@@ -14085,7 +13756,7 @@
         <v>146</v>
       </c>
       <c r="P7">
-        <v>1249.74</v>
+        <v>1239.18</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -14099,16 +13770,16 @@
         <v>0.719</v>
       </c>
       <c r="D8">
-        <v>0.2628</v>
+        <v>0.2621</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="G8">
-        <v>1178.25</v>
+        <v>1173.4</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -14123,7 +13794,7 @@
         <v>120.3600006103516</v>
       </c>
       <c r="L8">
-        <v>9.789999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="M8" t="s">
         <v>143</v>
@@ -14135,7 +13806,7 @@
         <v>145</v>
       </c>
       <c r="P8">
-        <v>1178.25</v>
+        <v>1173.4</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -14149,16 +13820,16 @@
         <v>0.6982</v>
       </c>
       <c r="D9">
-        <v>0.2518</v>
+        <v>0.257</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="G9">
-        <v>1159.71</v>
+        <v>1144.46</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -14173,7 +13844,7 @@
         <v>401.7200012207031</v>
       </c>
       <c r="L9">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="s">
         <v>143</v>
@@ -14185,7 +13856,7 @@
         <v>145</v>
       </c>
       <c r="P9">
-        <v>1159.71</v>
+        <v>1144.46</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -14199,7 +13870,7 @@
         <v>0.6973</v>
       </c>
       <c r="D10">
-        <v>0.2644</v>
+        <v>0.2649</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -14208,7 +13879,7 @@
         <v>4.31</v>
       </c>
       <c r="G10">
-        <v>1141.18</v>
+        <v>1133.94</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -14223,7 +13894,7 @@
         <v>591.010009765625</v>
       </c>
       <c r="L10">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="M10" t="s">
         <v>143</v>
@@ -14235,7 +13906,7 @@
         <v>145</v>
       </c>
       <c r="P10">
-        <v>1141.18</v>
+        <v>1133.94</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -14249,7 +13920,7 @@
         <v>0.6881</v>
       </c>
       <c r="D11">
-        <v>0.2607</v>
+        <v>0.2621</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -14258,7 +13929,7 @@
         <v>4.27</v>
       </c>
       <c r="G11">
-        <v>1130.59</v>
+        <v>1123.41</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -14273,7 +13944,7 @@
         <v>460.4700012207031</v>
       </c>
       <c r="L11">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="s">
         <v>143</v>
@@ -14285,21 +13956,21 @@
         <v>145</v>
       </c>
       <c r="P11">
-        <v>1130.59</v>
+        <v>1123.41</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12">
-        <v>0.6986</v>
+        <v>0.7124</v>
       </c>
       <c r="D12">
-        <v>0.2912</v>
+        <v>0.3042</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -14308,7 +13979,7 @@
         <v>4.16</v>
       </c>
       <c r="G12">
-        <v>1101.46</v>
+        <v>1094.47</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -14320,10 +13991,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>427.9200134277344</v>
+        <v>138.3899993896484</v>
       </c>
       <c r="L12">
-        <v>2.57</v>
+        <v>7.91</v>
       </c>
       <c r="M12" t="s">
         <v>143</v>
@@ -14335,30 +14006,30 @@
         <v>145</v>
       </c>
       <c r="P12">
-        <v>1101.46</v>
+        <v>1094.47</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.7124</v>
+        <v>0.6986</v>
       </c>
       <c r="D13">
-        <v>0.3051</v>
+        <v>0.2922</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="G13">
-        <v>1101.46</v>
+        <v>1091.84</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -14370,10 +14041,10 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>138.3899993896484</v>
+        <v>427.9200134277344</v>
       </c>
       <c r="L13">
-        <v>7.96</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="s">
         <v>143</v>
@@ -14385,7 +14056,7 @@
         <v>145</v>
       </c>
       <c r="P13">
-        <v>1101.46</v>
+        <v>1091.84</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -14399,7 +14070,7 @@
         <v>0.6953</v>
       </c>
       <c r="D14">
-        <v>0.2929</v>
+        <v>0.2933</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -14408,7 +14079,7 @@
         <v>4.13</v>
       </c>
       <c r="G14">
-        <v>1093.52</v>
+        <v>1086.58</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -14423,7 +14094,7 @@
         <v>562.1400146484375</v>
       </c>
       <c r="L14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M14" t="s">
         <v>143</v>
@@ -14435,7 +14106,7 @@
         <v>145</v>
       </c>
       <c r="P14">
-        <v>1093.52</v>
+        <v>1086.58</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -14449,7 +14120,7 @@
         <v>0.7392</v>
       </c>
       <c r="D15">
-        <v>0.3643</v>
+        <v>0.3635</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -14458,7 +14129,7 @@
         <v>3.95</v>
       </c>
       <c r="G15">
-        <v>1045.86</v>
+        <v>1039.22</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -14473,7 +14144,7 @@
         <v>465.2699890136719</v>
       </c>
       <c r="L15">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="M15" t="s">
         <v>143</v>
@@ -14485,7 +14156,7 @@
         <v>145</v>
       </c>
       <c r="P15">
-        <v>1045.86</v>
+        <v>1039.22</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -14499,7 +14170,7 @@
         <v>0.6959</v>
       </c>
       <c r="D16">
-        <v>0.3321</v>
+        <v>0.3314</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -14508,7 +14179,7 @@
         <v>3.91</v>
       </c>
       <c r="G16">
-        <v>1035.27</v>
+        <v>1028.7</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -14523,7 +14194,7 @@
         <v>390.8999938964844</v>
       </c>
       <c r="L16">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="M16" t="s">
         <v>143</v>
@@ -14535,7 +14206,7 @@
         <v>145</v>
       </c>
       <c r="P16">
-        <v>1035.27</v>
+        <v>1028.7</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -14549,7 +14220,7 @@
         <v>0.6833</v>
       </c>
       <c r="D17">
-        <v>0.3311</v>
+        <v>0.3306</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -14558,7 +14229,7 @@
         <v>3.84</v>
       </c>
       <c r="G17">
-        <v>1016.74</v>
+        <v>1010.28</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -14585,7 +14256,7 @@
         <v>145</v>
       </c>
       <c r="P17">
-        <v>1016.74</v>
+        <v>1010.28</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -14608,7 +14279,7 @@
         <v>3.83</v>
       </c>
       <c r="G18">
-        <v>1014.09</v>
+        <v>1007.65</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -14623,7 +14294,7 @@
         <v>73.55999755859375</v>
       </c>
       <c r="L18">
-        <v>13.79</v>
+        <v>13.7</v>
       </c>
       <c r="M18" t="s">
         <v>143</v>
@@ -14635,7 +14306,7 @@
         <v>145</v>
       </c>
       <c r="P18">
-        <v>1014.09</v>
+        <v>1007.65</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -14649,16 +14320,16 @@
         <v>0.7124</v>
       </c>
       <c r="D19">
-        <v>0.3639</v>
+        <v>0.3632</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="G19">
-        <v>1006.14</v>
+        <v>1002.39</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -14673,7 +14344,7 @@
         <v>260.5199890136719</v>
       </c>
       <c r="L19">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="s">
         <v>143</v>
@@ -14685,7 +14356,7 @@
         <v>145</v>
       </c>
       <c r="P19">
-        <v>1006.14</v>
+        <v>1002.39</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -14699,16 +14370,16 @@
         <v>0.7285</v>
       </c>
       <c r="D20">
-        <v>0.3852</v>
+        <v>0.3867</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="G20">
-        <v>995.55</v>
+        <v>986.61</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -14723,7 +14394,7 @@
         <v>392.1600036621094</v>
       </c>
       <c r="L20">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="M20" t="s">
         <v>143</v>
@@ -14735,7 +14406,7 @@
         <v>145</v>
       </c>
       <c r="P20">
-        <v>995.55</v>
+        <v>986.61</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -14749,16 +14420,16 @@
         <v>0.7141999999999999</v>
       </c>
       <c r="D21">
-        <v>0.4067</v>
+        <v>0.4056</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="G21">
-        <v>942.6</v>
+        <v>939.25</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -14773,7 +14444,7 @@
         <v>152.1600036621094</v>
       </c>
       <c r="L21">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="M21" t="s">
         <v>143</v>
@@ -14785,7 +14456,7 @@
         <v>145</v>
       </c>
       <c r="P21">
-        <v>942.6</v>
+        <v>939.25</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -14799,7 +14470,7 @@
         <v>0.6908</v>
       </c>
       <c r="D22">
-        <v>0.3937</v>
+        <v>0.3925</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -14808,7 +14479,7 @@
         <v>3.52</v>
       </c>
       <c r="G22">
-        <v>932.01</v>
+        <v>926.09</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -14823,7 +14494,7 @@
         <v>2139.3701171875</v>
       </c>
       <c r="L22">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="M22" t="s">
         <v>143</v>
@@ -14835,30 +14506,30 @@
         <v>145</v>
       </c>
       <c r="P22">
-        <v>932.01</v>
+        <v>926.09</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
       </c>
       <c r="C23">
-        <v>0.7493</v>
+        <v>0.7157</v>
       </c>
       <c r="D23">
-        <v>0.4516</v>
+        <v>0.427</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="G23">
-        <v>913.47</v>
+        <v>905.05</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -14870,10 +14541,10 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>289.5199890136719</v>
+        <v>644.9299926757812</v>
       </c>
       <c r="L23">
-        <v>3.16</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="s">
         <v>143</v>
@@ -14882,33 +14553,33 @@
         <v>1.2</v>
       </c>
       <c r="O23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P23">
-        <v>913.47</v>
+        <v>905.05</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
       </c>
       <c r="C24">
-        <v>0.7157</v>
+        <v>0.719</v>
       </c>
       <c r="D24">
-        <v>0.428</v>
+        <v>0.4461</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="G24">
-        <v>910.83</v>
+        <v>881.37</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -14920,10 +14591,10 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>644.9299926757812</v>
+        <v>204.6900024414062</v>
       </c>
       <c r="L24">
-        <v>1.41</v>
+        <v>4.31</v>
       </c>
       <c r="M24" t="s">
         <v>143</v>
@@ -14935,30 +14606,30 @@
         <v>145</v>
       </c>
       <c r="P24">
-        <v>910.83</v>
+        <v>881.37</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
         <v>18</v>
       </c>
       <c r="C25">
-        <v>0.719</v>
+        <v>0.7493</v>
       </c>
       <c r="D25">
-        <v>0.4473</v>
+        <v>0.467</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="G25">
-        <v>884.35</v>
+        <v>881.37</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -14970,10 +14641,10 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>204.6900024414062</v>
+        <v>289.5199890136719</v>
       </c>
       <c r="L25">
-        <v>4.32</v>
+        <v>3.04</v>
       </c>
       <c r="M25" t="s">
         <v>143</v>
@@ -14982,10 +14653,10 @@
         <v>1.2</v>
       </c>
       <c r="O25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P25">
-        <v>884.35</v>
+        <v>881.37</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -14999,16 +14670,16 @@
         <v>0.7254</v>
       </c>
       <c r="D26">
-        <v>0.4833</v>
+        <v>0.4818</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="G26">
-        <v>834.04</v>
+        <v>831.38</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -15023,7 +14694,7 @@
         <v>35.15000152587891</v>
       </c>
       <c r="L26">
-        <v>23.73</v>
+        <v>23.65</v>
       </c>
       <c r="M26" t="s">
         <v>143</v>
@@ -15035,7 +14706,7 @@
         <v>145</v>
       </c>
       <c r="P26">
-        <v>834.04</v>
+        <v>831.38</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -15049,7 +14720,7 @@
         <v>0.7076</v>
       </c>
       <c r="D27">
-        <v>0.5095</v>
+        <v>0.5104</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -15058,7 +14729,7 @@
         <v>2.91</v>
       </c>
       <c r="G27">
-        <v>770.49</v>
+        <v>765.61</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -15073,7 +14744,7 @@
         <v>236.1300048828125</v>
       </c>
       <c r="L27">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="M27" t="s">
         <v>143</v>
@@ -15085,7 +14756,7 @@
         <v>145</v>
       </c>
       <c r="P27">
-        <v>770.49</v>
+        <v>765.61</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -15099,16 +14770,16 @@
         <v>0.6989</v>
       </c>
       <c r="D28">
-        <v>0.5104</v>
+        <v>0.5102</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="G28">
-        <v>759.9</v>
+        <v>757.71</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -15123,7 +14794,7 @@
         <v>266.8800048828125</v>
       </c>
       <c r="L28">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="s">
         <v>143</v>
@@ -15135,7 +14806,7 @@
         <v>145</v>
       </c>
       <c r="P28">
-        <v>759.9</v>
+        <v>757.71</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -15149,16 +14820,16 @@
         <v>0.6932</v>
       </c>
       <c r="D29">
-        <v>0.5185</v>
+        <v>0.5168</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="G29">
-        <v>741.37</v>
+        <v>739.3</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -15185,7 +14856,7 @@
         <v>145</v>
       </c>
       <c r="P29">
-        <v>741.37</v>
+        <v>739.3</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -15199,16 +14870,16 @@
         <v>0.7342</v>
       </c>
       <c r="D30">
-        <v>0.5464</v>
+        <v>0.5451</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="G30">
-        <v>741.37</v>
+        <v>739.3</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -15223,7 +14894,7 @@
         <v>107.9199981689453</v>
       </c>
       <c r="L30">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
       <c r="M30" t="s">
         <v>143</v>
@@ -15235,7 +14906,7 @@
         <v>145</v>
       </c>
       <c r="P30">
-        <v>741.37</v>
+        <v>739.3</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -15249,7 +14920,7 @@
         <v>0.7222</v>
       </c>
       <c r="D31">
-        <v>0.5427999999999999</v>
+        <v>0.5412</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -15258,7 +14929,7 @@
         <v>2.78</v>
       </c>
       <c r="G31">
-        <v>736.0700000000001</v>
+        <v>731.4</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -15273,7 +14944,7 @@
         <v>227.3399963378906</v>
       </c>
       <c r="L31">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="M31" t="s">
         <v>143</v>
@@ -15285,30 +14956,30 @@
         <v>145</v>
       </c>
       <c r="P31">
-        <v>736.0700000000001</v>
+        <v>731.4</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
         <v>18</v>
       </c>
       <c r="C32">
-        <v>0.6993</v>
+        <v>0.7948</v>
       </c>
       <c r="D32">
-        <v>0.5448</v>
+        <v>0.2659</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>0.2575</v>
       </c>
       <c r="F32">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="G32">
-        <v>706.95</v>
+        <v>710.36</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -15320,10 +14991,10 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>935.8900146484375</v>
+        <v>208.1900024414062</v>
       </c>
       <c r="L32">
-        <v>0.76</v>
+        <v>3.41</v>
       </c>
       <c r="M32" t="s">
         <v>143</v>
@@ -15335,7 +15006,7 @@
         <v>145</v>
       </c>
       <c r="P32">
-        <v>706.95</v>
+        <v>710.36</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -15349,7 +15020,7 @@
         <v>0.699</v>
       </c>
       <c r="D33">
-        <v>0.5456</v>
+        <v>0.5457</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -15358,7 +15029,7 @@
         <v>2.67</v>
       </c>
       <c r="G33">
-        <v>706.95</v>
+        <v>702.46</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -15373,7 +15044,7 @@
         <v>324.8599853515625</v>
       </c>
       <c r="L33">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="M33" t="s">
         <v>143</v>
@@ -15385,30 +15056,30 @@
         <v>145</v>
       </c>
       <c r="P33">
-        <v>706.95</v>
+        <v>702.46</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
         <v>18</v>
       </c>
       <c r="C34">
-        <v>0.7936</v>
+        <v>0.6993</v>
       </c>
       <c r="D34">
-        <v>0.2656</v>
+        <v>0.5448</v>
       </c>
       <c r="E34">
-        <v>0.2586</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="G34">
-        <v>704.3</v>
+        <v>702.46</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -15420,10 +15091,10 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>208.1900024414062</v>
+        <v>935.8900146484375</v>
       </c>
       <c r="L34">
-        <v>3.38</v>
+        <v>0.75</v>
       </c>
       <c r="M34" t="s">
         <v>143</v>
@@ -15435,7 +15106,7 @@
         <v>145</v>
       </c>
       <c r="P34">
-        <v>704.3</v>
+        <v>702.46</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -15449,7 +15120,7 @@
         <v>0.7634</v>
       </c>
       <c r="D35">
-        <v>0.6667</v>
+        <v>0.6656</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -15458,7 +15129,7 @@
         <v>2.14</v>
       </c>
       <c r="G35">
-        <v>566.62</v>
+        <v>563.02</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -15473,7 +15144,7 @@
         <v>29.55999946594238</v>
       </c>
       <c r="L35">
-        <v>19.17</v>
+        <v>19.05</v>
       </c>
       <c r="M35" t="s">
         <v>143</v>
@@ -15485,7 +15156,7 @@
         <v>146</v>
       </c>
       <c r="P35">
-        <v>566.62</v>
+        <v>563.02</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -15499,16 +15170,16 @@
         <v>0.7092000000000001</v>
       </c>
       <c r="D36">
-        <v>0.6468</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="G36">
-        <v>558.6799999999999</v>
+        <v>557.76</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -15535,7 +15206,7 @@
         <v>145</v>
       </c>
       <c r="P36">
-        <v>558.6799999999999</v>
+        <v>557.76</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -15546,19 +15217,19 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>0.7662</v>
+        <v>0.7675</v>
       </c>
       <c r="D37">
-        <v>0.4868</v>
+        <v>0.487</v>
       </c>
       <c r="E37">
-        <v>0.2608</v>
+        <v>0.2578</v>
       </c>
       <c r="F37">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G37">
-        <v>473.95</v>
+        <v>478.83</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -15573,7 +15244,7 @@
         <v>475.5050048828125</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="s">
         <v>143</v>
@@ -15585,7 +15256,7 @@
         <v>145</v>
       </c>
       <c r="P37">
-        <v>473.95</v>
+        <v>478.83</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -15599,16 +15270,16 @@
         <v>0.6879</v>
       </c>
       <c r="D38">
-        <v>0.6955</v>
+        <v>0.6939</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G38">
-        <v>466</v>
+        <v>465.68</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -15635,7 +15306,7 @@
         <v>145</v>
       </c>
       <c r="P38">
-        <v>466</v>
+        <v>465.68</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -15649,7 +15320,7 @@
         <v>0.4461</v>
       </c>
       <c r="D39">
-        <v>0.1823</v>
+        <v>0.1824</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -15658,7 +15329,7 @@
         <v>1.75</v>
       </c>
       <c r="G39">
-        <v>463.36</v>
+        <v>460.42</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -15673,7 +15344,7 @@
         <v>282.25</v>
       </c>
       <c r="L39">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M39" t="s">
         <v>143</v>
@@ -15685,7 +15356,7 @@
         <v>148</v>
       </c>
       <c r="P39">
-        <v>463.36</v>
+        <v>460.42</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -15699,7 +15370,7 @@
         <v>0.4794</v>
       </c>
       <c r="D40">
-        <v>0.2554</v>
+        <v>0.2571</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -15708,7 +15379,7 @@
         <v>1.71</v>
       </c>
       <c r="G40">
-        <v>452.77</v>
+        <v>449.89</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -15723,7 +15394,7 @@
         <v>68.72000122070312</v>
       </c>
       <c r="L40">
-        <v>6.59</v>
+        <v>6.55</v>
       </c>
       <c r="M40" t="s">
         <v>143</v>
@@ -15735,7 +15406,7 @@
         <v>147</v>
       </c>
       <c r="P40">
-        <v>452.77</v>
+        <v>449.89</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -15749,7 +15420,7 @@
         <v>0.435</v>
       </c>
       <c r="D41">
-        <v>0.1854</v>
+        <v>0.1851</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -15758,7 +15429,7 @@
         <v>1.7</v>
       </c>
       <c r="G41">
-        <v>450.12</v>
+        <v>447.26</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -15773,7 +15444,7 @@
         <v>148.6699981689453</v>
       </c>
       <c r="L41">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="M41" t="s">
         <v>143</v>
@@ -15785,7 +15456,7 @@
         <v>148</v>
       </c>
       <c r="P41">
-        <v>450.12</v>
+        <v>447.26</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -15796,19 +15467,19 @@
         <v>18</v>
       </c>
       <c r="C42">
-        <v>0.7996</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="D42">
-        <v>0.6777</v>
+        <v>0.6761</v>
       </c>
       <c r="E42">
-        <v>0.17</v>
+        <v>0.1691</v>
       </c>
       <c r="F42">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G42">
-        <v>434.23</v>
+        <v>436.74</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -15823,7 +15494,7 @@
         <v>98.44999694824219</v>
       </c>
       <c r="L42">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="M42" t="s">
         <v>143</v>
@@ -15835,7 +15506,7 @@
         <v>145</v>
       </c>
       <c r="P42">
-        <v>434.23</v>
+        <v>436.74</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -15849,7 +15520,7 @@
         <v>0.444</v>
       </c>
       <c r="D43">
-        <v>0.2399</v>
+        <v>0.2393</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -15858,7 +15529,7 @@
         <v>1.62</v>
       </c>
       <c r="G43">
-        <v>428.94</v>
+        <v>426.21</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -15873,7 +15544,7 @@
         <v>99.33000183105469</v>
       </c>
       <c r="L43">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="M43" t="s">
         <v>143</v>
@@ -15885,7 +15556,7 @@
         <v>147</v>
       </c>
       <c r="P43">
-        <v>428.94</v>
+        <v>426.21</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -15899,7 +15570,7 @@
         <v>0.4437</v>
       </c>
       <c r="D44">
-        <v>0.2377</v>
+        <v>0.2373</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -15908,7 +15579,7 @@
         <v>1.62</v>
       </c>
       <c r="G44">
-        <v>428.94</v>
+        <v>426.21</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -15923,7 +15594,7 @@
         <v>88.76999664306641</v>
       </c>
       <c r="L44">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="s">
         <v>143</v>
@@ -15935,7 +15606,7 @@
         <v>148</v>
       </c>
       <c r="P44">
-        <v>428.94</v>
+        <v>426.21</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -15949,16 +15620,16 @@
         <v>0.699</v>
       </c>
       <c r="D45">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G45">
-        <v>410.4</v>
+        <v>410.43</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -15985,7 +15656,7 @@
         <v>145</v>
       </c>
       <c r="P45">
-        <v>410.4</v>
+        <v>410.43</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -15999,7 +15670,7 @@
         <v>0.4611</v>
       </c>
       <c r="D46">
-        <v>0.3226</v>
+        <v>0.3225</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -16008,7 +15679,7 @@
         <v>1.5</v>
       </c>
       <c r="G46">
-        <v>397.16</v>
+        <v>394.64</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -16023,7 +15694,7 @@
         <v>851.4000244140625</v>
       </c>
       <c r="L46">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="M46" t="s">
         <v>143</v>
@@ -16035,7 +15706,7 @@
         <v>147</v>
       </c>
       <c r="P46">
-        <v>397.16</v>
+        <v>394.64</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -16049,16 +15720,16 @@
         <v>0.4322</v>
       </c>
       <c r="D47">
-        <v>0.2924</v>
+        <v>0.2918</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G47">
-        <v>386.57</v>
+        <v>386.75</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -16085,7 +15756,7 @@
         <v>148</v>
       </c>
       <c r="P47">
-        <v>386.57</v>
+        <v>386.75</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -16099,7 +15770,7 @@
         <v>0.4491</v>
       </c>
       <c r="D48">
-        <v>0.3663</v>
+        <v>0.3655</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -16108,7 +15779,7 @@
         <v>1.37</v>
       </c>
       <c r="G48">
-        <v>362.74</v>
+        <v>360.44</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -16123,7 +15794,7 @@
         <v>15.23999977111816</v>
       </c>
       <c r="L48">
-        <v>23.8</v>
+        <v>23.65</v>
       </c>
       <c r="M48" t="s">
         <v>143</v>
@@ -16135,7 +15806,7 @@
         <v>147</v>
       </c>
       <c r="P48">
-        <v>362.74</v>
+        <v>360.44</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -16149,7 +15820,7 @@
         <v>0.4091</v>
       </c>
       <c r="D49">
-        <v>0.3048</v>
+        <v>0.3042</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -16158,7 +15829,7 @@
         <v>1.36</v>
       </c>
       <c r="G49">
-        <v>360.09</v>
+        <v>357.81</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -16173,7 +15844,7 @@
         <v>75</v>
       </c>
       <c r="L49">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="M49" t="s">
         <v>143</v>
@@ -16185,7 +15856,7 @@
         <v>148</v>
       </c>
       <c r="P49">
-        <v>360.09</v>
+        <v>357.81</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -16199,16 +15870,16 @@
         <v>0.7333</v>
       </c>
       <c r="D50">
-        <v>0.7839</v>
+        <v>0.7816</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G50">
-        <v>352.15</v>
+        <v>355.18</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -16223,7 +15894,7 @@
         <v>14.06999969482422</v>
       </c>
       <c r="L50">
-        <v>25.03</v>
+        <v>25.24</v>
       </c>
       <c r="M50" t="s">
         <v>143</v>
@@ -16235,7 +15906,7 @@
         <v>145</v>
       </c>
       <c r="P50">
-        <v>352.15</v>
+        <v>355.18</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -16249,7 +15920,7 @@
         <v>0.4449</v>
       </c>
       <c r="D51">
-        <v>0.3837</v>
+        <v>0.383</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -16258,7 +15929,7 @@
         <v>1.32</v>
       </c>
       <c r="G51">
-        <v>349.5</v>
+        <v>347.29</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -16273,7 +15944,7 @@
         <v>237.8800048828125</v>
       </c>
       <c r="L51">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M51" t="s">
         <v>143</v>
@@ -16285,7 +15956,7 @@
         <v>148</v>
       </c>
       <c r="P51">
-        <v>349.5</v>
+        <v>347.29</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -16299,7 +15970,7 @@
         <v>0.4287</v>
       </c>
       <c r="D52">
-        <v>0.3842</v>
+        <v>0.3848</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -16308,7 +15979,7 @@
         <v>1.27</v>
       </c>
       <c r="G52">
-        <v>336.26</v>
+        <v>334.13</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -16323,7 +15994,7 @@
         <v>178.9199981689453</v>
       </c>
       <c r="L52">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="M52" t="s">
         <v>143</v>
@@ -16335,7 +16006,7 @@
         <v>148</v>
       </c>
       <c r="P52">
-        <v>336.26</v>
+        <v>334.13</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -16349,7 +16020,7 @@
         <v>0.4237</v>
       </c>
       <c r="D53">
-        <v>0.3876</v>
+        <v>0.3867</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -16358,7 +16029,7 @@
         <v>1.24</v>
       </c>
       <c r="G53">
-        <v>328.32</v>
+        <v>326.24</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -16373,7 +16044,7 @@
         <v>40.77000045776367</v>
       </c>
       <c r="L53">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="M53" t="s">
         <v>143</v>
@@ -16385,21 +16056,21 @@
         <v>148</v>
       </c>
       <c r="P53">
-        <v>328.32</v>
+        <v>326.24</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="C54">
-        <v>0.4147</v>
+        <v>0.716</v>
       </c>
       <c r="D54">
-        <v>0.3907</v>
+        <v>0.7983</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -16408,7 +16079,7 @@
         <v>1.21</v>
       </c>
       <c r="G54">
-        <v>320.38</v>
+        <v>318.34</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -16420,10 +16091,10 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>44.65000152587891</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="L54">
-        <v>7.18</v>
+        <v>3.38</v>
       </c>
       <c r="M54" t="s">
         <v>143</v>
@@ -16432,33 +16103,33 @@
         <v>1.2</v>
       </c>
       <c r="O54" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P54">
-        <v>320.38</v>
+        <v>318.34</v>
       </c>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="C55">
-        <v>0.716</v>
+        <v>0.4147</v>
       </c>
       <c r="D55">
-        <v>0.8008999999999999</v>
+        <v>0.3899</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="G55">
-        <v>317.73</v>
+        <v>318.34</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -16470,10 +16141,10 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>94.30999755859375</v>
+        <v>44.65000152587891</v>
       </c>
       <c r="L55">
-        <v>3.37</v>
+        <v>7.13</v>
       </c>
       <c r="M55" t="s">
         <v>143</v>
@@ -16482,24 +16153,24 @@
         <v>1.2</v>
       </c>
       <c r="O55" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P55">
-        <v>317.73</v>
+        <v>318.34</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B56" t="s">
         <v>133</v>
       </c>
       <c r="C56">
-        <v>0.4328</v>
+        <v>0.4055</v>
       </c>
       <c r="D56">
-        <v>0.4371</v>
+        <v>0.4009</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -16508,7 +16179,7 @@
         <v>1.17</v>
       </c>
       <c r="G56">
-        <v>309.79</v>
+        <v>307.82</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -16520,10 +16191,10 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>251.6499938964844</v>
+        <v>277.489990234375</v>
       </c>
       <c r="L56">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="M56" t="s">
         <v>143</v>
@@ -16535,30 +16206,30 @@
         <v>148</v>
       </c>
       <c r="P56">
-        <v>309.79</v>
+        <v>307.82</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
         <v>133</v>
       </c>
       <c r="C57">
-        <v>0.4055</v>
+        <v>0.4328</v>
       </c>
       <c r="D57">
-        <v>0.4019</v>
+        <v>0.4408</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G57">
-        <v>309.79</v>
+        <v>305.19</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -16570,10 +16241,10 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>277.489990234375</v>
+        <v>251.6499938964844</v>
       </c>
       <c r="L57">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="M57" t="s">
         <v>143</v>
@@ -16585,30 +16256,30 @@
         <v>148</v>
       </c>
       <c r="P57">
-        <v>309.79</v>
+        <v>305.19</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
         <v>133</v>
       </c>
       <c r="C58">
-        <v>0.4401</v>
+        <v>0.4135</v>
       </c>
       <c r="D58">
-        <v>0.5273</v>
+        <v>0.4976</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G58">
-        <v>264.77</v>
+        <v>260.46</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -16620,10 +16291,10 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>42.52000045776367</v>
+        <v>205.8099975585938</v>
       </c>
       <c r="L58">
-        <v>6.23</v>
+        <v>1.27</v>
       </c>
       <c r="M58" t="s">
         <v>143</v>
@@ -16635,21 +16306,21 @@
         <v>148</v>
       </c>
       <c r="P58">
-        <v>264.77</v>
+        <v>260.46</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B59" t="s">
         <v>133</v>
       </c>
       <c r="C59">
-        <v>0.4135</v>
+        <v>0.4401</v>
       </c>
       <c r="D59">
-        <v>0.4988</v>
+        <v>0.5321</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -16658,7 +16329,7 @@
         <v>0.99</v>
       </c>
       <c r="G59">
-        <v>262.13</v>
+        <v>260.46</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -16670,10 +16341,10 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>205.8099975585938</v>
+        <v>42.52000045776367</v>
       </c>
       <c r="L59">
-        <v>1.27</v>
+        <v>6.13</v>
       </c>
       <c r="M59" t="s">
         <v>143</v>
@@ -16685,7 +16356,7 @@
         <v>148</v>
       </c>
       <c r="P59">
-        <v>262.13</v>
+        <v>260.46</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -16699,7 +16370,7 @@
         <v>0.4361</v>
       </c>
       <c r="D60">
-        <v>0.5315</v>
+        <v>0.5311</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -16708,7 +16379,7 @@
         <v>0.98</v>
       </c>
       <c r="G60">
-        <v>259.48</v>
+        <v>257.83</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -16723,7 +16394,7 @@
         <v>65.75</v>
       </c>
       <c r="L60">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="M60" t="s">
         <v>143</v>
@@ -16735,7 +16406,7 @@
         <v>148</v>
       </c>
       <c r="P60">
-        <v>259.48</v>
+        <v>257.83</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -16749,7 +16420,7 @@
         <v>0.4204</v>
       </c>
       <c r="D61">
-        <v>0.519</v>
+        <v>0.5179</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -16758,7 +16429,7 @@
         <v>0.97</v>
       </c>
       <c r="G61">
-        <v>256.83</v>
+        <v>255.2</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -16773,7 +16444,7 @@
         <v>140.2299957275391</v>
       </c>
       <c r="L61">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="M61" t="s">
         <v>143</v>
@@ -16785,7 +16456,7 @@
         <v>148</v>
       </c>
       <c r="P61">
-        <v>256.83</v>
+        <v>255.2</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -16799,7 +16470,7 @@
         <v>0.4086</v>
       </c>
       <c r="D62">
-        <v>0.5091</v>
+        <v>0.5085</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -16808,7 +16479,7 @@
         <v>0.96</v>
       </c>
       <c r="G62">
-        <v>254.18</v>
+        <v>252.57</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -16823,7 +16494,7 @@
         <v>109.7099990844727</v>
       </c>
       <c r="L62">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M62" t="s">
         <v>143</v>
@@ -16835,7 +16506,7 @@
         <v>148</v>
       </c>
       <c r="P62">
-        <v>254.18</v>
+        <v>252.57</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -16846,19 +16517,19 @@
         <v>133</v>
       </c>
       <c r="C63">
-        <v>0.4208</v>
+        <v>0.4209</v>
       </c>
       <c r="D63">
-        <v>0.3374</v>
+        <v>0.3367</v>
       </c>
       <c r="E63">
-        <v>0.2076</v>
+        <v>0.2073</v>
       </c>
       <c r="F63">
         <v>0.96</v>
       </c>
       <c r="G63">
-        <v>254.18</v>
+        <v>252.57</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -16885,7 +16556,7 @@
         <v>148</v>
       </c>
       <c r="P63">
-        <v>254.18</v>
+        <v>252.57</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -16899,7 +16570,7 @@
         <v>0.429</v>
       </c>
       <c r="D64">
-        <v>0.5538</v>
+        <v>0.5524</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -16908,7 +16579,7 @@
         <v>0.92</v>
       </c>
       <c r="G64">
-        <v>243.59</v>
+        <v>242.05</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -16923,7 +16594,7 @@
         <v>21.68000030517578</v>
       </c>
       <c r="L64">
-        <v>11.24</v>
+        <v>11.16</v>
       </c>
       <c r="M64" t="s">
         <v>143</v>
@@ -16935,30 +16606,30 @@
         <v>148</v>
       </c>
       <c r="P64">
-        <v>243.59</v>
+        <v>242.05</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s">
         <v>133</v>
       </c>
       <c r="C65">
-        <v>0.4157</v>
+        <v>0.4262</v>
       </c>
       <c r="D65">
-        <v>0.5492</v>
+        <v>0.5578</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G65">
-        <v>238.3</v>
+        <v>239.42</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -16970,10 +16641,10 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>48.81999969482422</v>
+        <v>10.75</v>
       </c>
       <c r="L65">
-        <v>4.88</v>
+        <v>22.27</v>
       </c>
       <c r="M65" t="s">
         <v>143</v>
@@ -16985,21 +16656,21 @@
         <v>148</v>
       </c>
       <c r="P65">
-        <v>238.3</v>
+        <v>239.42</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
         <v>133</v>
       </c>
       <c r="C66">
-        <v>0.4262</v>
+        <v>0.4157</v>
       </c>
       <c r="D66">
-        <v>0.5590000000000001</v>
+        <v>0.5492</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -17008,7 +16679,7 @@
         <v>0.9</v>
       </c>
       <c r="G66">
-        <v>238.3</v>
+        <v>236.79</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -17020,10 +16691,10 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>10.75</v>
+        <v>48.81999969482422</v>
       </c>
       <c r="L66">
-        <v>22.17</v>
+        <v>4.85</v>
       </c>
       <c r="M66" t="s">
         <v>143</v>
@@ -17035,7 +16706,7 @@
         <v>148</v>
       </c>
       <c r="P66">
-        <v>238.3</v>
+        <v>236.79</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -17049,7 +16720,7 @@
         <v>0.4134</v>
       </c>
       <c r="D67">
-        <v>0.5483</v>
+        <v>0.548</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -17058,7 +16729,7 @@
         <v>0.89</v>
       </c>
       <c r="G67">
-        <v>235.65</v>
+        <v>234.15</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -17073,7 +16744,7 @@
         <v>3.220000028610229</v>
       </c>
       <c r="L67">
-        <v>73.18000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="M67" t="s">
         <v>143</v>
@@ -17085,7 +16756,7 @@
         <v>148</v>
       </c>
       <c r="P67">
-        <v>235.65</v>
+        <v>234.15</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -17099,7 +16770,7 @@
         <v>0.4226</v>
       </c>
       <c r="D68">
-        <v>0.5955</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -17108,7 +16779,7 @@
         <v>0.82</v>
       </c>
       <c r="G68">
-        <v>217.12</v>
+        <v>215.74</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -17123,7 +16794,7 @@
         <v>106.9700012207031</v>
       </c>
       <c r="L68">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="M68" t="s">
         <v>143</v>
@@ -17135,7 +16806,7 @@
         <v>148</v>
       </c>
       <c r="P68">
-        <v>217.12</v>
+        <v>215.74</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -17149,7 +16820,7 @@
         <v>0.4272</v>
       </c>
       <c r="D69">
-        <v>0.6105</v>
+        <v>0.61</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -17158,7 +16829,7 @@
         <v>0.8</v>
       </c>
       <c r="G69">
-        <v>211.82</v>
+        <v>210.48</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -17185,30 +16856,30 @@
         <v>148</v>
       </c>
       <c r="P69">
-        <v>211.82</v>
+        <v>210.48</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B70" t="s">
         <v>133</v>
       </c>
       <c r="C70">
-        <v>0.4566</v>
+        <v>0.4376</v>
       </c>
       <c r="D70">
-        <v>0.6411</v>
+        <v>0.3501</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="F70">
         <v>0.79</v>
       </c>
       <c r="G70">
-        <v>209.17</v>
+        <v>207.84</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -17220,10 +16891,10 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>125.8399963378906</v>
+        <v>396.6799926757812</v>
       </c>
       <c r="L70">
-        <v>1.66</v>
+        <v>0.52</v>
       </c>
       <c r="M70" t="s">
         <v>143</v>
@@ -17232,33 +16903,33 @@
         <v>1.2</v>
       </c>
       <c r="O70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P70">
-        <v>209.17</v>
+        <v>207.84</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
         <v>133</v>
       </c>
       <c r="C71">
-        <v>0.4368</v>
+        <v>0.4566</v>
       </c>
       <c r="D71">
-        <v>0.3497</v>
+        <v>0.6397</v>
       </c>
       <c r="E71">
-        <v>0.2816</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G71">
-        <v>206.52</v>
+        <v>207.84</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -17270,10 +16941,10 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>396.6799926757812</v>
+        <v>125.8399963378906</v>
       </c>
       <c r="L71">
-        <v>0.52</v>
+        <v>1.65</v>
       </c>
       <c r="M71" t="s">
         <v>143</v>
@@ -17282,10 +16953,10 @@
         <v>1.2</v>
       </c>
       <c r="O71" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P71">
-        <v>206.52</v>
+        <v>207.84</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -17299,7 +16970,7 @@
         <v>0.4497</v>
       </c>
       <c r="D72">
-        <v>0.6395</v>
+        <v>0.6379</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -17308,7 +16979,7 @@
         <v>0.78</v>
       </c>
       <c r="G72">
-        <v>206.52</v>
+        <v>205.21</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -17323,7 +16994,7 @@
         <v>7.019999980926514</v>
       </c>
       <c r="L72">
-        <v>29.42</v>
+        <v>29.23</v>
       </c>
       <c r="M72" t="s">
         <v>143</v>
@@ -17335,7 +17006,7 @@
         <v>147</v>
       </c>
       <c r="P72">
-        <v>206.52</v>
+        <v>205.21</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -17349,7 +17020,7 @@
         <v>0.4058</v>
       </c>
       <c r="D73">
-        <v>0.6409</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -17358,7 +17029,7 @@
         <v>0.7</v>
       </c>
       <c r="G73">
-        <v>185.34</v>
+        <v>184.17</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -17373,7 +17044,7 @@
         <v>6.75</v>
       </c>
       <c r="L73">
-        <v>27.46</v>
+        <v>27.28</v>
       </c>
       <c r="M73" t="s">
         <v>143</v>
@@ -17385,7 +17056,7 @@
         <v>148</v>
       </c>
       <c r="P73">
-        <v>185.34</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -17399,7 +17070,7 @@
         <v>0.4143</v>
       </c>
       <c r="D74">
-        <v>0.6587</v>
+        <v>0.6575</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -17408,7 +17079,7 @@
         <v>0.68</v>
       </c>
       <c r="G74">
-        <v>180.05</v>
+        <v>178.9</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -17423,7 +17094,7 @@
         <v>520.8400268554688</v>
       </c>
       <c r="L74">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="M74" t="s">
         <v>143</v>
@@ -17435,7 +17106,7 @@
         <v>148</v>
       </c>
       <c r="P74">
-        <v>180.05</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -17449,7 +17120,7 @@
         <v>0.4236</v>
       </c>
       <c r="D75">
-        <v>0.6864</v>
+        <v>0.6854</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -17458,7 +17129,7 @@
         <v>0.64</v>
       </c>
       <c r="G75">
-        <v>169.46</v>
+        <v>168.38</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -17473,7 +17144,7 @@
         <v>3.990000009536743</v>
       </c>
       <c r="L75">
-        <v>42.47</v>
+        <v>42.2</v>
       </c>
       <c r="M75" t="s">
         <v>143</v>
@@ -17485,7 +17156,7 @@
         <v>148</v>
       </c>
       <c r="P75">
-        <v>169.46</v>
+        <v>168.38</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -17499,16 +17170,16 @@
         <v>0.4036</v>
       </c>
       <c r="D76">
-        <v>0.6782</v>
+        <v>0.6938</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="G76">
-        <v>164.16</v>
+        <v>155.23</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -17523,7 +17194,7 @@
         <v>40.63999938964844</v>
       </c>
       <c r="L76">
-        <v>4.04</v>
+        <v>3.82</v>
       </c>
       <c r="M76" t="s">
         <v>143</v>
@@ -17535,7 +17206,7 @@
         <v>148</v>
       </c>
       <c r="P76">
-        <v>164.16</v>
+        <v>155.23</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -17549,16 +17220,16 @@
         <v>0.4149</v>
       </c>
       <c r="D77">
-        <v>0.7629</v>
+        <v>0.761</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="G77">
-        <v>124.44</v>
+        <v>126.29</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -17573,7 +17244,7 @@
         <v>56.68999862670898</v>
       </c>
       <c r="L77">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="M77" t="s">
         <v>143</v>
@@ -17585,30 +17256,30 @@
         <v>148</v>
       </c>
       <c r="P77">
-        <v>124.44</v>
+        <v>126.29</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
         <v>133</v>
       </c>
       <c r="C78">
-        <v>0.4198</v>
+        <v>0.4272</v>
       </c>
       <c r="D78">
-        <v>0.6236</v>
+        <v>0.7827</v>
       </c>
       <c r="E78">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>0.45</v>
       </c>
       <c r="G78">
-        <v>119.15</v>
+        <v>118.39</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -17620,10 +17291,10 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>83.76999664306641</v>
+        <v>10</v>
       </c>
       <c r="L78">
-        <v>1.42</v>
+        <v>11.84</v>
       </c>
       <c r="M78" t="s">
         <v>143</v>
@@ -17635,30 +17306,30 @@
         <v>148</v>
       </c>
       <c r="P78">
-        <v>119.15</v>
+        <v>118.39</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
         <v>133</v>
       </c>
       <c r="C79">
-        <v>0.4272</v>
+        <v>0.4181</v>
       </c>
       <c r="D79">
-        <v>0.7844</v>
+        <v>0.6248</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>0.2912</v>
       </c>
       <c r="F79">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G79">
-        <v>116.5</v>
+        <v>113.13</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -17670,10 +17341,10 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>10</v>
+        <v>83.76999664306641</v>
       </c>
       <c r="L79">
-        <v>11.65</v>
+        <v>1.35</v>
       </c>
       <c r="M79" t="s">
         <v>143</v>
@@ -17685,7 +17356,7 @@
         <v>148</v>
       </c>
       <c r="P79">
-        <v>116.5</v>
+        <v>113.13</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -17696,19 +17367,19 @@
         <v>18</v>
       </c>
       <c r="C80">
-        <v>0.789</v>
+        <v>0.7883</v>
       </c>
       <c r="D80">
-        <v>0.9613</v>
+        <v>0.9583</v>
       </c>
       <c r="E80">
-        <v>0.104</v>
+        <v>0.1042</v>
       </c>
       <c r="F80">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G80">
-        <v>50.31</v>
+        <v>52.62</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -17723,7 +17394,7 @@
         <v>9.409999847412109</v>
       </c>
       <c r="L80">
-        <v>5.35</v>
+        <v>5.59</v>
       </c>
       <c r="M80" t="s">
         <v>143</v>
@@ -17735,7 +17406,7 @@
         <v>146</v>
       </c>
       <c r="P80">
-        <v>50.31</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -17749,7 +17420,7 @@
         <v>0.3932</v>
       </c>
       <c r="D81">
-        <v>0.5943000000000001</v>
+        <v>0.5933</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -17758,7 +17429,7 @@
         <v>0.19</v>
       </c>
       <c r="G81">
-        <v>50.31</v>
+        <v>49.99</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -17773,7 +17444,7 @@
         <v>10.78999996185303</v>
       </c>
       <c r="L81">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
       <c r="M81" t="s">
         <v>143</v>
@@ -17785,7 +17456,7 @@
         <v>148</v>
       </c>
       <c r="P81">
-        <v>50.31</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -17799,7 +17470,7 @@
         <v>0.398</v>
       </c>
       <c r="D82">
-        <v>0.6439</v>
+        <v>0.6423</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -17808,7 +17479,7 @@
         <v>0.17</v>
       </c>
       <c r="G82">
-        <v>45.01</v>
+        <v>44.73</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -17835,7 +17506,7 @@
         <v>148</v>
       </c>
       <c r="P82">
-        <v>45.01</v>
+        <v>44.73</v>
       </c>
     </row>
   </sheetData>
@@ -17845,7 +17516,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -17885,191 +17556,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>1.57</v>
       </c>
       <c r="C2">
-        <v>3507.54</v>
+        <v>904.96</v>
       </c>
       <c r="D2">
-        <v>339.67</v>
+        <v>78.05</v>
       </c>
       <c r="E2">
-        <v>-90.81</v>
+        <v>-96.56999999999999</v>
       </c>
       <c r="F2">
-        <v>0.9789</v>
+        <v>0.9857</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0.6132</v>
+        <v>0.6324</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3">
-        <v>80</v>
-      </c>
-      <c r="C3">
-        <v>752.8</v>
-      </c>
-      <c r="D3">
-        <v>47.49</v>
-      </c>
-      <c r="E3">
-        <v>-1.78</v>
-      </c>
-      <c r="F3">
-        <v>0.4461</v>
-      </c>
-      <c r="G3">
-        <v>0.6945</v>
-      </c>
-      <c r="H3">
-        <v>0.1286</v>
-      </c>
-      <c r="I3">
-        <v>0.0331</v>
-      </c>
-      <c r="J3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>44</v>
-      </c>
-      <c r="C4">
-        <v>414.04</v>
-      </c>
-      <c r="D4">
-        <v>26.12</v>
-      </c>
-      <c r="E4">
-        <v>-1.78</v>
-      </c>
-      <c r="F4">
-        <v>0.4342</v>
-      </c>
-      <c r="G4">
-        <v>0.6945</v>
-      </c>
-      <c r="H4">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="I4">
-        <v>0.0331</v>
-      </c>
-      <c r="J4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>31</v>
-      </c>
-      <c r="C5">
-        <v>2596.87</v>
-      </c>
-      <c r="D5">
-        <v>607.1</v>
-      </c>
-      <c r="E5">
-        <v>-1.54</v>
-      </c>
-      <c r="F5">
-        <v>0.3835</v>
-      </c>
-      <c r="G5">
-        <v>0.6937</v>
-      </c>
-      <c r="H5">
-        <v>0.453</v>
-      </c>
-      <c r="I5">
-        <v>0.1891</v>
-      </c>
-      <c r="J5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>21.54</v>
-      </c>
-      <c r="D6">
-        <v>9.82</v>
-      </c>
-      <c r="E6">
-        <v>2.19</v>
-      </c>
-      <c r="F6">
-        <v>0.3949</v>
-      </c>
-      <c r="G6">
-        <v>0.6808999999999999</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>60.44</v>
-      </c>
-      <c r="C7">
-        <v>650.98</v>
-      </c>
-      <c r="D7">
-        <v>310.91</v>
-      </c>
-      <c r="E7">
-        <v>2.43</v>
-      </c>
-      <c r="F7">
-        <v>0.5821</v>
-      </c>
-      <c r="G7">
-        <v>0.6801</v>
-      </c>
-      <c r="H7">
-        <v>0.8374</v>
-      </c>
-      <c r="I7">
-        <v>0.0331</v>
-      </c>
-      <c r="J7" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/prod-portfolio_intelligence.xlsx
+++ b/data/exports/prod-portfolio_intelligence.xlsx
@@ -15382,7 +15382,7 @@
         <v>0.4922</v>
       </c>
       <c r="D40">
-        <v>0.2634</v>
+        <v>0.2638</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0.4619</v>
       </c>
       <c r="D48">
-        <v>0.3267</v>
+        <v>0.327</v>
       </c>
       <c r="E48">
         <v>0</v>
